--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_calibration_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-4\api\templates\device_calibration_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1D520B-D518-4A95-92B2-F99DBFC8569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Калібрування пристрою" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -83,7 +82,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -175,16 +177,38 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -193,7 +217,12 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -569,7 +598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E501"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -630,13 +659,13 @@
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="8" t="str">
         <f ca="1">IF(ISNUMBER(D8),IF(D8-TODAY()&lt;0,"OVERDUE",INT(D8-TODAY())),"")</f>
         <v/>
       </c>
@@ -2615,7 +2644,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:E100000">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>IF(ISNUMBER($D8),$D8-TODAY()&lt;0,0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-4\api\templates\device_calibration_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_calibration_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB46E06C-B75B-824B-AFF7-E81A371583CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Калібрування пристрою" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
@@ -110,12 +111,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -132,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,6 +151,19 @@
       </top>
       <bottom style="medium">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -175,18 +187,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6B9B8"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -209,18 +228,11 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6B9B8"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="2"/>
+      <tableStyleElement type="headerRow" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -598,44 +610,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E501"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" customWidth="1"/>
-    <col min="2" max="2" width="26.3984375" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.09765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -652,1999 +664,1999 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="9" t="str">
         <f ca="1">IF(ISNUMBER(D8),IF(D8-TODAY()&lt;0,"OVERDUE",INT(D8-TODAY())),"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C9"/>
       <c r="D9"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C10"/>
       <c r="D10"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C11"/>
       <c r="D11"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C12"/>
       <c r="D12"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C13"/>
       <c r="D13"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C14"/>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15"/>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C16"/>
       <c r="D16"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17"/>
       <c r="D17"/>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18"/>
       <c r="D18"/>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19"/>
       <c r="D19"/>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20"/>
       <c r="D20"/>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21"/>
       <c r="D21"/>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C22"/>
       <c r="D22"/>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C23"/>
       <c r="D23"/>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C24"/>
       <c r="D24"/>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C25"/>
       <c r="D25"/>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C26"/>
       <c r="D26"/>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C27"/>
       <c r="D27"/>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C28"/>
       <c r="D28"/>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C29"/>
       <c r="D29"/>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C30"/>
       <c r="D30"/>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C31"/>
       <c r="D31"/>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C32"/>
       <c r="D32"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C33"/>
       <c r="D33"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C34"/>
       <c r="D34"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35"/>
       <c r="D35"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C36"/>
       <c r="D36"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C37"/>
       <c r="D37"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C38"/>
       <c r="D38"/>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C40"/>
       <c r="D40"/>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C41"/>
       <c r="D41"/>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C42"/>
       <c r="D42"/>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C43"/>
       <c r="D43"/>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C44"/>
       <c r="D44"/>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C45"/>
       <c r="D45"/>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C46"/>
       <c r="D46"/>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C47"/>
       <c r="D47"/>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C48"/>
       <c r="D48"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49"/>
       <c r="D49"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50"/>
       <c r="D50"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51"/>
       <c r="D51"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52"/>
       <c r="D52"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53"/>
       <c r="D53"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54"/>
       <c r="D54"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55"/>
       <c r="D55"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C56"/>
       <c r="D56"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C57"/>
       <c r="D57"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C58"/>
       <c r="D58"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C59"/>
       <c r="D59"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C60"/>
       <c r="D60"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C61"/>
       <c r="D61"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C62"/>
       <c r="D62"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C63"/>
       <c r="D63"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C64"/>
       <c r="D64"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C65"/>
       <c r="D65"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C66"/>
       <c r="D66"/>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C67"/>
       <c r="D67"/>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C68"/>
       <c r="D68"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C69"/>
       <c r="D69"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C70"/>
       <c r="D70"/>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C71"/>
       <c r="D71"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C72"/>
       <c r="D72"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C73"/>
       <c r="D73"/>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C74"/>
       <c r="D74"/>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C75"/>
       <c r="D75"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C76"/>
       <c r="D76"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C77"/>
       <c r="D77"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C78"/>
       <c r="D78"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C79"/>
       <c r="D79"/>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C80"/>
       <c r="D80"/>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C81"/>
       <c r="D81"/>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C82"/>
       <c r="D82"/>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C83"/>
       <c r="D83"/>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C84"/>
       <c r="D84"/>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C85"/>
       <c r="D85"/>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C86"/>
       <c r="D86"/>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C87"/>
       <c r="D87"/>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C88"/>
       <c r="D88"/>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C89"/>
       <c r="D89"/>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C90"/>
       <c r="D90"/>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C91"/>
       <c r="D91"/>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C92"/>
       <c r="D92"/>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C93"/>
       <c r="D93"/>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C94"/>
       <c r="D94"/>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C95"/>
       <c r="D95"/>
     </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C96"/>
       <c r="D96"/>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C97"/>
       <c r="D97"/>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C98"/>
       <c r="D98"/>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C99"/>
       <c r="D99"/>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C100"/>
       <c r="D100"/>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C101"/>
       <c r="D101"/>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C102"/>
       <c r="D102"/>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C103"/>
       <c r="D103"/>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C104"/>
       <c r="D104"/>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C105"/>
       <c r="D105"/>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C106"/>
       <c r="D106"/>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C107"/>
       <c r="D107"/>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C108"/>
       <c r="D108"/>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C109"/>
       <c r="D109"/>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C110"/>
       <c r="D110"/>
     </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C111"/>
       <c r="D111"/>
     </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C112"/>
       <c r="D112"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C113"/>
       <c r="D113"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C114"/>
       <c r="D114"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C115"/>
       <c r="D115"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C116"/>
       <c r="D116"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C117"/>
       <c r="D117"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C118"/>
       <c r="D118"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C119"/>
       <c r="D119"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C120"/>
       <c r="D120"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C121"/>
       <c r="D121"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C122"/>
       <c r="D122"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C123"/>
       <c r="D123"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C124"/>
       <c r="D124"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C125"/>
       <c r="D125"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C126"/>
       <c r="D126"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C127"/>
       <c r="D127"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C128"/>
       <c r="D128"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C129"/>
       <c r="D129"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C130"/>
       <c r="D130"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C131"/>
       <c r="D131"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C132"/>
       <c r="D132"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C133"/>
       <c r="D133"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C134"/>
       <c r="D134"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C135"/>
       <c r="D135"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C136"/>
       <c r="D136"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C137"/>
       <c r="D137"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C138"/>
       <c r="D138"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C139"/>
       <c r="D139"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C140"/>
       <c r="D140"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C141"/>
       <c r="D141"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C142"/>
       <c r="D142"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C143"/>
       <c r="D143"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C144"/>
       <c r="D144"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C145"/>
       <c r="D145"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C146"/>
       <c r="D146"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C147"/>
       <c r="D147"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C148"/>
       <c r="D148"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C149"/>
       <c r="D149"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C150"/>
       <c r="D150"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C151"/>
       <c r="D151"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C152"/>
       <c r="D152"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C153"/>
       <c r="D153"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C154"/>
       <c r="D154"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C155"/>
       <c r="D155"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C156"/>
       <c r="D156"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C157"/>
       <c r="D157"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C158"/>
       <c r="D158"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C159"/>
       <c r="D159"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C160"/>
       <c r="D160"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C161"/>
       <c r="D161"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C162"/>
       <c r="D162"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C163"/>
       <c r="D163"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C164"/>
       <c r="D164"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C165"/>
       <c r="D165"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C166"/>
       <c r="D166"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C167"/>
       <c r="D167"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C168"/>
       <c r="D168"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C169"/>
       <c r="D169"/>
     </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C170"/>
       <c r="D170"/>
     </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C171"/>
       <c r="D171"/>
     </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C172"/>
       <c r="D172"/>
     </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C173"/>
       <c r="D173"/>
     </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C174"/>
       <c r="D174"/>
     </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C175"/>
       <c r="D175"/>
     </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C176"/>
       <c r="D176"/>
     </row>
-    <row r="177" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C177"/>
       <c r="D177"/>
     </row>
-    <row r="178" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C178"/>
       <c r="D178"/>
     </row>
-    <row r="179" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C179"/>
       <c r="D179"/>
     </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C180"/>
       <c r="D180"/>
     </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C181"/>
       <c r="D181"/>
     </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C182"/>
       <c r="D182"/>
     </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C183"/>
       <c r="D183"/>
     </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C184"/>
       <c r="D184"/>
     </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C185"/>
       <c r="D185"/>
     </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C186"/>
       <c r="D186"/>
     </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C187"/>
       <c r="D187"/>
     </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C188"/>
       <c r="D188"/>
     </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C189"/>
       <c r="D189"/>
     </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C190"/>
       <c r="D190"/>
     </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C191"/>
       <c r="D191"/>
     </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C192"/>
       <c r="D192"/>
     </row>
-    <row r="193" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C193"/>
       <c r="D193"/>
     </row>
-    <row r="194" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C194"/>
       <c r="D194"/>
     </row>
-    <row r="195" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C195"/>
       <c r="D195"/>
     </row>
-    <row r="196" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C196"/>
       <c r="D196"/>
     </row>
-    <row r="197" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C197"/>
       <c r="D197"/>
     </row>
-    <row r="198" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C198"/>
       <c r="D198"/>
     </row>
-    <row r="199" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C199"/>
       <c r="D199"/>
     </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C200"/>
       <c r="D200"/>
     </row>
-    <row r="201" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C201"/>
       <c r="D201"/>
     </row>
-    <row r="202" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C202"/>
       <c r="D202"/>
     </row>
-    <row r="203" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C203"/>
       <c r="D203"/>
     </row>
-    <row r="204" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C204"/>
       <c r="D204"/>
     </row>
-    <row r="205" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C205"/>
       <c r="D205"/>
     </row>
-    <row r="206" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C206"/>
       <c r="D206"/>
     </row>
-    <row r="207" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C207"/>
       <c r="D207"/>
     </row>
-    <row r="208" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C208"/>
       <c r="D208"/>
     </row>
-    <row r="209" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C209"/>
       <c r="D209"/>
     </row>
-    <row r="210" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C210"/>
       <c r="D210"/>
     </row>
-    <row r="211" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C211"/>
       <c r="D211"/>
     </row>
-    <row r="212" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C212"/>
       <c r="D212"/>
     </row>
-    <row r="213" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C213"/>
       <c r="D213"/>
     </row>
-    <row r="214" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C214"/>
       <c r="D214"/>
     </row>
-    <row r="215" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C215"/>
       <c r="D215"/>
     </row>
-    <row r="216" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C216"/>
       <c r="D216"/>
     </row>
-    <row r="217" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C217"/>
       <c r="D217"/>
     </row>
-    <row r="218" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C218"/>
       <c r="D218"/>
     </row>
-    <row r="219" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C219"/>
       <c r="D219"/>
     </row>
-    <row r="220" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C220"/>
       <c r="D220"/>
     </row>
-    <row r="221" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C221"/>
       <c r="D221"/>
     </row>
-    <row r="222" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C222"/>
       <c r="D222"/>
     </row>
-    <row r="223" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C223"/>
       <c r="D223"/>
     </row>
-    <row r="224" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C224"/>
       <c r="D224"/>
     </row>
-    <row r="225" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C225"/>
       <c r="D225"/>
     </row>
-    <row r="226" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C226"/>
       <c r="D226"/>
     </row>
-    <row r="227" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C227"/>
       <c r="D227"/>
     </row>
-    <row r="228" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C228"/>
       <c r="D228"/>
     </row>
-    <row r="229" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C229"/>
       <c r="D229"/>
     </row>
-    <row r="230" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C230"/>
       <c r="D230"/>
     </row>
-    <row r="231" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C231"/>
       <c r="D231"/>
     </row>
-    <row r="232" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C232"/>
       <c r="D232"/>
     </row>
-    <row r="233" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C233"/>
       <c r="D233"/>
     </row>
-    <row r="234" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C234"/>
       <c r="D234"/>
     </row>
-    <row r="235" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C235"/>
       <c r="D235"/>
     </row>
-    <row r="236" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C236"/>
       <c r="D236"/>
     </row>
-    <row r="237" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C237"/>
       <c r="D237"/>
     </row>
-    <row r="238" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C238"/>
       <c r="D238"/>
     </row>
-    <row r="239" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C239"/>
       <c r="D239"/>
     </row>
-    <row r="240" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C240"/>
       <c r="D240"/>
     </row>
-    <row r="241" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C241"/>
       <c r="D241"/>
     </row>
-    <row r="242" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C242"/>
       <c r="D242"/>
     </row>
-    <row r="243" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C243"/>
       <c r="D243"/>
     </row>
-    <row r="244" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C244"/>
       <c r="D244"/>
     </row>
-    <row r="245" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C245"/>
       <c r="D245"/>
     </row>
-    <row r="246" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C246"/>
       <c r="D246"/>
     </row>
-    <row r="247" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C247"/>
       <c r="D247"/>
     </row>
-    <row r="248" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C248"/>
       <c r="D248"/>
     </row>
-    <row r="249" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C249"/>
       <c r="D249"/>
     </row>
-    <row r="250" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C250"/>
       <c r="D250"/>
     </row>
-    <row r="251" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C251"/>
       <c r="D251"/>
     </row>
-    <row r="252" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C252"/>
       <c r="D252"/>
     </row>
-    <row r="253" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C253"/>
       <c r="D253"/>
     </row>
-    <row r="254" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C254"/>
       <c r="D254"/>
     </row>
-    <row r="255" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C255"/>
       <c r="D255"/>
     </row>
-    <row r="256" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C256"/>
       <c r="D256"/>
     </row>
-    <row r="257" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C257"/>
       <c r="D257"/>
     </row>
-    <row r="258" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C258"/>
       <c r="D258"/>
     </row>
-    <row r="259" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C259"/>
       <c r="D259"/>
     </row>
-    <row r="260" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C260"/>
       <c r="D260"/>
     </row>
-    <row r="261" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C261"/>
       <c r="D261"/>
     </row>
-    <row r="262" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C262"/>
       <c r="D262"/>
     </row>
-    <row r="263" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C263"/>
       <c r="D263"/>
     </row>
-    <row r="264" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C264"/>
       <c r="D264"/>
     </row>
-    <row r="265" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C265"/>
       <c r="D265"/>
     </row>
-    <row r="266" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C266"/>
       <c r="D266"/>
     </row>
-    <row r="267" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C267"/>
       <c r="D267"/>
     </row>
-    <row r="268" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C268"/>
       <c r="D268"/>
     </row>
-    <row r="269" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C269"/>
       <c r="D269"/>
     </row>
-    <row r="270" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C270"/>
       <c r="D270"/>
     </row>
-    <row r="271" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C271"/>
       <c r="D271"/>
     </row>
-    <row r="272" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C272"/>
       <c r="D272"/>
     </row>
-    <row r="273" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C273"/>
       <c r="D273"/>
     </row>
-    <row r="274" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C274"/>
       <c r="D274"/>
     </row>
-    <row r="275" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C275"/>
       <c r="D275"/>
     </row>
-    <row r="276" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C276"/>
       <c r="D276"/>
     </row>
-    <row r="277" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C277"/>
       <c r="D277"/>
     </row>
-    <row r="278" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C278"/>
       <c r="D278"/>
     </row>
-    <row r="279" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C279"/>
       <c r="D279"/>
     </row>
-    <row r="280" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C280"/>
       <c r="D280"/>
     </row>
-    <row r="281" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C281"/>
       <c r="D281"/>
     </row>
-    <row r="282" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C282"/>
       <c r="D282"/>
     </row>
-    <row r="283" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C283"/>
       <c r="D283"/>
     </row>
-    <row r="284" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C284"/>
       <c r="D284"/>
     </row>
-    <row r="285" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C285"/>
       <c r="D285"/>
     </row>
-    <row r="286" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C286"/>
       <c r="D286"/>
     </row>
-    <row r="287" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C287"/>
       <c r="D287"/>
     </row>
-    <row r="288" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C288"/>
       <c r="D288"/>
     </row>
-    <row r="289" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C289"/>
       <c r="D289"/>
     </row>
-    <row r="290" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C290"/>
       <c r="D290"/>
     </row>
-    <row r="291" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C291"/>
       <c r="D291"/>
     </row>
-    <row r="292" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C292"/>
       <c r="D292"/>
     </row>
-    <row r="293" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C293"/>
       <c r="D293"/>
     </row>
-    <row r="294" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C294"/>
       <c r="D294"/>
     </row>
-    <row r="295" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C295"/>
       <c r="D295"/>
     </row>
-    <row r="296" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C296"/>
       <c r="D296"/>
     </row>
-    <row r="297" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C297"/>
       <c r="D297"/>
     </row>
-    <row r="298" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C298"/>
       <c r="D298"/>
     </row>
-    <row r="299" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C299"/>
       <c r="D299"/>
     </row>
-    <row r="300" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C300"/>
       <c r="D300"/>
     </row>
-    <row r="301" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C301"/>
       <c r="D301"/>
     </row>
-    <row r="302" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C302"/>
       <c r="D302"/>
     </row>
-    <row r="303" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C303"/>
       <c r="D303"/>
     </row>
-    <row r="304" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C304"/>
       <c r="D304"/>
     </row>
-    <row r="305" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C305"/>
       <c r="D305"/>
     </row>
-    <row r="306" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C306"/>
       <c r="D306"/>
     </row>
-    <row r="307" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C307"/>
       <c r="D307"/>
     </row>
-    <row r="308" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C308"/>
       <c r="D308"/>
     </row>
-    <row r="309" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C309"/>
       <c r="D309"/>
     </row>
-    <row r="310" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C310"/>
       <c r="D310"/>
     </row>
-    <row r="311" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C311"/>
       <c r="D311"/>
     </row>
-    <row r="312" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C312"/>
       <c r="D312"/>
     </row>
-    <row r="313" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C313"/>
       <c r="D313"/>
     </row>
-    <row r="314" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C314"/>
       <c r="D314"/>
     </row>
-    <row r="315" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C315"/>
       <c r="D315"/>
     </row>
-    <row r="316" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C316"/>
       <c r="D316"/>
     </row>
-    <row r="317" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C317"/>
       <c r="D317"/>
     </row>
-    <row r="318" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C318"/>
       <c r="D318"/>
     </row>
-    <row r="319" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C319"/>
       <c r="D319"/>
     </row>
-    <row r="320" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C320"/>
       <c r="D320"/>
     </row>
-    <row r="321" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C321"/>
       <c r="D321"/>
     </row>
-    <row r="322" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C322"/>
       <c r="D322"/>
     </row>
-    <row r="323" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C323"/>
       <c r="D323"/>
     </row>
-    <row r="324" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C324"/>
       <c r="D324"/>
     </row>
-    <row r="325" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C325"/>
       <c r="D325"/>
     </row>
-    <row r="326" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C326"/>
       <c r="D326"/>
     </row>
-    <row r="327" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C327"/>
       <c r="D327"/>
     </row>
-    <row r="328" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C328"/>
       <c r="D328"/>
     </row>
-    <row r="329" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C329"/>
       <c r="D329"/>
     </row>
-    <row r="330" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C330"/>
       <c r="D330"/>
     </row>
-    <row r="331" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C331"/>
       <c r="D331"/>
     </row>
-    <row r="332" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C332"/>
       <c r="D332"/>
     </row>
-    <row r="333" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C333"/>
       <c r="D333"/>
     </row>
-    <row r="334" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C334"/>
       <c r="D334"/>
     </row>
-    <row r="335" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C335"/>
       <c r="D335"/>
     </row>
-    <row r="336" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C336"/>
       <c r="D336"/>
     </row>
-    <row r="337" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C337"/>
       <c r="D337"/>
     </row>
-    <row r="338" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C338"/>
       <c r="D338"/>
     </row>
-    <row r="339" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C339"/>
       <c r="D339"/>
     </row>
-    <row r="340" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C340"/>
       <c r="D340"/>
     </row>
-    <row r="341" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C341"/>
       <c r="D341"/>
     </row>
-    <row r="342" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C342"/>
       <c r="D342"/>
     </row>
-    <row r="343" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C343"/>
       <c r="D343"/>
     </row>
-    <row r="344" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C344"/>
       <c r="D344"/>
     </row>
-    <row r="345" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C345"/>
       <c r="D345"/>
     </row>
-    <row r="346" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C346"/>
       <c r="D346"/>
     </row>
-    <row r="347" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C347"/>
       <c r="D347"/>
     </row>
-    <row r="348" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C348"/>
       <c r="D348"/>
     </row>
-    <row r="349" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C349"/>
       <c r="D349"/>
     </row>
-    <row r="350" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C350"/>
       <c r="D350"/>
     </row>
-    <row r="351" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C351"/>
       <c r="D351"/>
     </row>
-    <row r="352" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C352"/>
       <c r="D352"/>
     </row>
-    <row r="353" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C353"/>
       <c r="D353"/>
     </row>
-    <row r="354" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C354"/>
       <c r="D354"/>
     </row>
-    <row r="355" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C355"/>
       <c r="D355"/>
     </row>
-    <row r="356" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C356"/>
       <c r="D356"/>
     </row>
-    <row r="357" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C357"/>
       <c r="D357"/>
     </row>
-    <row r="358" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C358"/>
       <c r="D358"/>
     </row>
-    <row r="359" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C359"/>
       <c r="D359"/>
     </row>
-    <row r="360" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C360"/>
       <c r="D360"/>
     </row>
-    <row r="361" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C361"/>
       <c r="D361"/>
     </row>
-    <row r="362" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C362"/>
       <c r="D362"/>
     </row>
-    <row r="363" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C363"/>
       <c r="D363"/>
     </row>
-    <row r="364" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C364"/>
       <c r="D364"/>
     </row>
-    <row r="365" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C365"/>
       <c r="D365"/>
     </row>
-    <row r="366" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C366"/>
       <c r="D366"/>
     </row>
-    <row r="367" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C367"/>
       <c r="D367"/>
     </row>
-    <row r="368" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C368"/>
       <c r="D368"/>
     </row>
-    <row r="369" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C369"/>
       <c r="D369"/>
     </row>
-    <row r="370" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C370"/>
       <c r="D370"/>
     </row>
-    <row r="371" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C371"/>
       <c r="D371"/>
     </row>
-    <row r="372" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C372"/>
       <c r="D372"/>
     </row>
-    <row r="373" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C373"/>
       <c r="D373"/>
     </row>
-    <row r="374" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C374"/>
       <c r="D374"/>
     </row>
-    <row r="375" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C375"/>
       <c r="D375"/>
     </row>
-    <row r="376" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C376"/>
       <c r="D376"/>
     </row>
-    <row r="377" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C377"/>
       <c r="D377"/>
     </row>
-    <row r="378" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C378"/>
       <c r="D378"/>
     </row>
-    <row r="379" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C379"/>
       <c r="D379"/>
     </row>
-    <row r="380" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C380"/>
       <c r="D380"/>
     </row>
-    <row r="381" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C381"/>
       <c r="D381"/>
     </row>
-    <row r="382" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C382"/>
       <c r="D382"/>
     </row>
-    <row r="383" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C383"/>
       <c r="D383"/>
     </row>
-    <row r="384" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C384"/>
       <c r="D384"/>
     </row>
-    <row r="385" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C385"/>
       <c r="D385"/>
     </row>
-    <row r="386" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C386"/>
       <c r="D386"/>
     </row>
-    <row r="387" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C387"/>
       <c r="D387"/>
     </row>
-    <row r="388" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C388"/>
       <c r="D388"/>
     </row>
-    <row r="389" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C389"/>
       <c r="D389"/>
     </row>
-    <row r="390" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C390"/>
       <c r="D390"/>
     </row>
-    <row r="391" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C391"/>
       <c r="D391"/>
     </row>
-    <row r="392" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C392"/>
       <c r="D392"/>
     </row>
-    <row r="393" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C393"/>
       <c r="D393"/>
     </row>
-    <row r="394" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C394"/>
       <c r="D394"/>
     </row>
-    <row r="395" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C395"/>
       <c r="D395"/>
     </row>
-    <row r="396" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C396"/>
       <c r="D396"/>
     </row>
-    <row r="397" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C397"/>
       <c r="D397"/>
     </row>
-    <row r="398" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C398"/>
       <c r="D398"/>
     </row>
-    <row r="399" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C399"/>
       <c r="D399"/>
     </row>
-    <row r="400" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C400"/>
       <c r="D400"/>
     </row>
-    <row r="401" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C401"/>
       <c r="D401"/>
     </row>
-    <row r="402" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C402"/>
       <c r="D402"/>
     </row>
-    <row r="403" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C403"/>
       <c r="D403"/>
     </row>
-    <row r="404" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C404"/>
       <c r="D404"/>
     </row>
-    <row r="405" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C405"/>
       <c r="D405"/>
     </row>
-    <row r="406" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C406"/>
       <c r="D406"/>
     </row>
-    <row r="407" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C407"/>
       <c r="D407"/>
     </row>
-    <row r="408" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C408"/>
       <c r="D408"/>
     </row>
-    <row r="409" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C409"/>
       <c r="D409"/>
     </row>
-    <row r="410" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C410"/>
       <c r="D410"/>
     </row>
-    <row r="411" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C411"/>
       <c r="D411"/>
     </row>
-    <row r="412" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C412"/>
       <c r="D412"/>
     </row>
-    <row r="413" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C413"/>
       <c r="D413"/>
     </row>
-    <row r="414" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C414"/>
       <c r="D414"/>
     </row>
-    <row r="415" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C415"/>
       <c r="D415"/>
     </row>
-    <row r="416" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C416"/>
       <c r="D416"/>
     </row>
-    <row r="417" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C417"/>
       <c r="D417"/>
     </row>
-    <row r="418" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C418"/>
       <c r="D418"/>
     </row>
-    <row r="419" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C419"/>
       <c r="D419"/>
     </row>
-    <row r="420" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C420"/>
       <c r="D420"/>
     </row>
-    <row r="421" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C421"/>
       <c r="D421"/>
     </row>
-    <row r="422" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C422"/>
       <c r="D422"/>
     </row>
-    <row r="423" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C423"/>
       <c r="D423"/>
     </row>
-    <row r="424" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C424"/>
       <c r="D424"/>
     </row>
-    <row r="425" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C425"/>
       <c r="D425"/>
     </row>
-    <row r="426" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C426"/>
       <c r="D426"/>
     </row>
-    <row r="427" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C427"/>
       <c r="D427"/>
     </row>
-    <row r="428" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C428"/>
       <c r="D428"/>
     </row>
-    <row r="429" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C429"/>
       <c r="D429"/>
     </row>
-    <row r="430" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C430"/>
       <c r="D430"/>
     </row>
-    <row r="431" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C431"/>
       <c r="D431"/>
     </row>
-    <row r="432" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C432"/>
       <c r="D432"/>
     </row>
-    <row r="433" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C433"/>
       <c r="D433"/>
     </row>
-    <row r="434" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C434"/>
       <c r="D434"/>
     </row>
-    <row r="435" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C435"/>
       <c r="D435"/>
     </row>
-    <row r="436" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C436"/>
       <c r="D436"/>
     </row>
-    <row r="437" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C437"/>
       <c r="D437"/>
     </row>
-    <row r="438" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C438"/>
       <c r="D438"/>
     </row>
-    <row r="439" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C439"/>
       <c r="D439"/>
     </row>
-    <row r="440" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C440"/>
       <c r="D440"/>
     </row>
-    <row r="441" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C441"/>
       <c r="D441"/>
     </row>
-    <row r="442" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C442"/>
       <c r="D442"/>
     </row>
-    <row r="443" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C443"/>
       <c r="D443"/>
     </row>
-    <row r="444" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C444"/>
       <c r="D444"/>
     </row>
-    <row r="445" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C445"/>
       <c r="D445"/>
     </row>
-    <row r="446" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C446"/>
       <c r="D446"/>
     </row>
-    <row r="447" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C447"/>
       <c r="D447"/>
     </row>
-    <row r="448" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C448"/>
       <c r="D448"/>
     </row>
-    <row r="449" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C449"/>
       <c r="D449"/>
     </row>
-    <row r="450" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C450"/>
       <c r="D450"/>
     </row>
-    <row r="451" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C451"/>
       <c r="D451"/>
     </row>
-    <row r="452" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C452"/>
       <c r="D452"/>
     </row>
-    <row r="453" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C453"/>
       <c r="D453"/>
     </row>
-    <row r="454" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C454"/>
       <c r="D454"/>
     </row>
-    <row r="455" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C455"/>
       <c r="D455"/>
     </row>
-    <row r="456" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C456"/>
       <c r="D456"/>
     </row>
-    <row r="457" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C457"/>
       <c r="D457"/>
     </row>
-    <row r="458" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C458"/>
       <c r="D458"/>
     </row>
-    <row r="459" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C459"/>
       <c r="D459"/>
     </row>
-    <row r="460" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C460"/>
       <c r="D460"/>
     </row>
-    <row r="461" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C461"/>
       <c r="D461"/>
     </row>
-    <row r="462" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C462"/>
       <c r="D462"/>
     </row>
-    <row r="463" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C463"/>
       <c r="D463"/>
     </row>
-    <row r="464" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C464"/>
       <c r="D464"/>
     </row>
-    <row r="465" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C465"/>
       <c r="D465"/>
     </row>
-    <row r="466" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C466"/>
       <c r="D466"/>
     </row>
-    <row r="467" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C467"/>
       <c r="D467"/>
     </row>
-    <row r="468" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C468"/>
       <c r="D468"/>
     </row>
-    <row r="469" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C469"/>
       <c r="D469"/>
     </row>
-    <row r="470" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C470"/>
       <c r="D470"/>
     </row>
-    <row r="471" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C471"/>
       <c r="D471"/>
     </row>
-    <row r="472" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C472"/>
       <c r="D472"/>
     </row>
-    <row r="473" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C473"/>
       <c r="D473"/>
     </row>
-    <row r="474" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C474"/>
       <c r="D474"/>
     </row>
-    <row r="475" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C475"/>
       <c r="D475"/>
     </row>
-    <row r="476" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C476"/>
       <c r="D476"/>
     </row>
-    <row r="477" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C477"/>
       <c r="D477"/>
     </row>
-    <row r="478" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C478"/>
       <c r="D478"/>
     </row>
-    <row r="479" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C479"/>
       <c r="D479"/>
     </row>
-    <row r="480" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C480"/>
       <c r="D480"/>
     </row>
-    <row r="481" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C481"/>
       <c r="D481"/>
     </row>
-    <row r="482" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C482"/>
       <c r="D482"/>
     </row>
-    <row r="483" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C483"/>
       <c r="D483"/>
     </row>
-    <row r="484" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C484"/>
       <c r="D484"/>
     </row>
-    <row r="485" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C485"/>
       <c r="D485"/>
     </row>
-    <row r="486" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C486"/>
       <c r="D486"/>
     </row>
-    <row r="487" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C487"/>
       <c r="D487"/>
     </row>
-    <row r="488" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C488"/>
       <c r="D488"/>
     </row>
-    <row r="489" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C489"/>
       <c r="D489"/>
     </row>
-    <row r="490" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C490"/>
       <c r="D490"/>
     </row>
-    <row r="491" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C491"/>
       <c r="D491"/>
     </row>
-    <row r="492" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C492"/>
       <c r="D492"/>
     </row>
-    <row r="493" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C493"/>
       <c r="D493"/>
     </row>
-    <row r="494" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C494"/>
       <c r="D494"/>
     </row>
-    <row r="495" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C495"/>
       <c r="D495"/>
     </row>
-    <row r="496" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C496"/>
       <c r="D496"/>
     </row>
-    <row r="497" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C497"/>
       <c r="D497"/>
     </row>
-    <row r="498" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C498"/>
       <c r="D498"/>
     </row>
-    <row r="499" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C499"/>
       <c r="D499"/>
     </row>
-    <row r="500" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C500"/>
       <c r="D500"/>
     </row>
-    <row r="501" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C501"/>
       <c r="D501"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:E100000">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>IF(ISNUMBER($D8),$D8-TODAY()&lt;0,0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED682D6-73B7-DE4D-AA13-980ABD65EE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Калібрування пристрою" state="visible" r:id="rId4"/>
+    <sheet name="Калібрування пристрою" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,45 +81,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -131,10 +145,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -181,7 +203,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6B9B8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6B9B8"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -498,9 +534,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F501"/>
-  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -510,38 +546,38 @@
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>7</v>
@@ -556,12 +592,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
@@ -572,2482 +608,2000 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="9">
-        <f>IF(ISNUMBER(E8),IF(E8-TODAY()&lt;0,"OVERDUE",INT(E8-TODAY())),"")</f>
+      <c r="F8" s="9" t="str">
+        <f ca="1">IF(ISNUMBER(E8),IF(E8-TODAY()&lt;0,"OVERDUE",INT(E8-TODAY())),"")</f>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="1"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E9" s="1"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D10" s="1"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E10" s="1"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="1"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E11" s="1"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="1"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="1"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E13" s="1"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E14" s="1"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E15" s="1"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E17" s="1"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D18" s="1"/>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="1"/>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E19" s="1"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D20" s="1"/>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E20" s="1"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="1"/>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D22" s="1"/>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E22" s="1"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="1"/>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E23" s="1"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="1"/>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="1"/>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E25" s="1"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="1"/>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E26" s="1"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="1"/>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="1"/>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="1"/>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E29" s="1"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D30" s="1"/>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E30" s="1"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D31" s="1"/>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="1"/>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E32" s="1"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D33" s="1"/>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D34" s="1"/>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E34" s="1"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D35" s="1"/>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E35" s="1"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D36" s="1"/>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E36" s="1"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D37" s="1"/>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D38" s="1"/>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E38" s="1"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D39" s="1"/>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E39" s="1"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="1"/>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E40" s="1"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="1"/>
+    <row r="41" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E41" s="1"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="1"/>
+    <row r="42" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E42" s="1"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D43" s="1"/>
+    <row r="43" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E43" s="1"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D44" s="1"/>
+    <row r="44" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E44" s="1"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D45" s="1"/>
+    <row r="45" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E45" s="1"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D46" s="1"/>
+    <row r="46" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E46" s="1"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D47" s="1"/>
+    <row r="47" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E47" s="1"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D48" s="1"/>
+    <row r="48" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E48" s="1"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D49" s="1"/>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E49" s="1"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D50" s="1"/>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E50" s="1"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D51" s="1"/>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E51" s="1"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D52" s="1"/>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E52" s="1"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D53" s="1"/>
+    <row r="53" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E53" s="1"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D54" s="1"/>
+    <row r="54" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E54" s="1"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D55" s="1"/>
+    <row r="55" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E55" s="1"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D56" s="1"/>
+    <row r="56" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E56" s="1"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="1"/>
+    <row r="57" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E57" s="1"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D58" s="1"/>
+    <row r="58" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E58" s="1"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="1"/>
+    <row r="59" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E59" s="1"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="1"/>
+    <row r="60" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E60" s="1"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="1"/>
+    <row r="61" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E61" s="1"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="1"/>
+    <row r="62" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E62" s="1"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="1"/>
+    <row r="63" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E63" s="1"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D64" s="1"/>
+    <row r="64" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E64" s="1"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D65" s="1"/>
+    <row r="65" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E65" s="1"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D66" s="1"/>
+    <row r="66" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E66" s="1"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="1"/>
+    <row r="67" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E67" s="1"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="1"/>
+    <row r="68" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E68" s="1"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="1"/>
+    <row r="69" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E69" s="1"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="1"/>
+    <row r="70" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E70" s="1"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="1"/>
+    <row r="71" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E71" s="1"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="1"/>
+    <row r="72" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E72" s="1"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D73" s="1"/>
+    <row r="73" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E73" s="1"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D74" s="1"/>
+    <row r="74" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E74" s="1"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D75" s="1"/>
+    <row r="75" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E75" s="1"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D76" s="1"/>
+    <row r="76" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E76" s="1"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D77" s="1"/>
+    <row r="77" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E77" s="1"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D78" s="1"/>
+    <row r="78" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E78" s="1"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D79" s="1"/>
+    <row r="79" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E79" s="1"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D80" s="1"/>
+    <row r="80" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E80" s="1"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="1"/>
+    <row r="81" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E81" s="1"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="1"/>
+    <row r="82" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E82" s="1"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="1"/>
+    <row r="83" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E83" s="1"/>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="1"/>
+    <row r="84" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E84" s="1"/>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="1"/>
+    <row r="85" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E85" s="1"/>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="1"/>
+    <row r="86" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E86" s="1"/>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="1"/>
+    <row r="87" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E87" s="1"/>
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="1"/>
+    <row r="88" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E88" s="1"/>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="1"/>
+    <row r="89" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E89" s="1"/>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="1"/>
+    <row r="90" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E90" s="1"/>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D91" s="1"/>
+    <row r="91" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E91" s="1"/>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D92" s="1"/>
+    <row r="92" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E92" s="1"/>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D93" s="1"/>
+    <row r="93" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E93" s="1"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="1"/>
+    <row r="94" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E94" s="1"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="1"/>
+    <row r="95" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E95" s="1"/>
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="1"/>
+    <row r="96" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E96" s="1"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="1"/>
+    <row r="97" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E97" s="1"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="1"/>
+    <row r="98" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E98" s="1"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="1"/>
+    <row r="99" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E99" s="1"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="1"/>
+    <row r="100" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E100" s="1"/>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="1"/>
+    <row r="101" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E101" s="1"/>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D102" s="1"/>
+    <row r="102" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E102" s="1"/>
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D103" s="1"/>
+    <row r="103" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E103" s="1"/>
       <c r="F103" s="2"/>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D104" s="1"/>
+    <row r="104" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E104" s="1"/>
       <c r="F104" s="2"/>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D105" s="1"/>
+    <row r="105" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E105" s="1"/>
       <c r="F105" s="2"/>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D106" s="1"/>
+    <row r="106" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E106" s="1"/>
       <c r="F106" s="2"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D107" s="1"/>
+    <row r="107" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E107" s="1"/>
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D108" s="1"/>
+    <row r="108" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E108" s="1"/>
       <c r="F108" s="2"/>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D109" s="1"/>
+    <row r="109" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E109" s="1"/>
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D110" s="1"/>
+    <row r="110" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E110" s="1"/>
       <c r="F110" s="2"/>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D111" s="1"/>
+    <row r="111" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E111" s="1"/>
       <c r="F111" s="2"/>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D112" s="1"/>
+    <row r="112" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E112" s="1"/>
       <c r="F112" s="2"/>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D113" s="1"/>
+    <row r="113" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E113" s="1"/>
       <c r="F113" s="2"/>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D114" s="1"/>
+    <row r="114" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E114" s="1"/>
       <c r="F114" s="2"/>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D115" s="1"/>
+    <row r="115" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E115" s="1"/>
       <c r="F115" s="2"/>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D116" s="1"/>
+    <row r="116" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E116" s="1"/>
       <c r="F116" s="2"/>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D117" s="1"/>
+    <row r="117" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E117" s="1"/>
       <c r="F117" s="2"/>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D118" s="1"/>
+    <row r="118" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E118" s="1"/>
       <c r="F118" s="2"/>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D119" s="1"/>
+    <row r="119" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E119" s="1"/>
       <c r="F119" s="2"/>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D120" s="1"/>
+    <row r="120" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E120" s="1"/>
       <c r="F120" s="2"/>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D121" s="1"/>
+    <row r="121" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E121" s="1"/>
       <c r="F121" s="2"/>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D122" s="1"/>
+    <row r="122" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E122" s="1"/>
       <c r="F122" s="2"/>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D123" s="1"/>
+    <row r="123" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E123" s="1"/>
       <c r="F123" s="2"/>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D124" s="1"/>
+    <row r="124" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E124" s="1"/>
       <c r="F124" s="2"/>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D125" s="1"/>
+    <row r="125" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E125" s="1"/>
       <c r="F125" s="2"/>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D126" s="1"/>
+    <row r="126" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E126" s="1"/>
       <c r="F126" s="2"/>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D127" s="1"/>
+    <row r="127" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E127" s="1"/>
       <c r="F127" s="2"/>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D128" s="1"/>
+    <row r="128" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E128" s="1"/>
       <c r="F128" s="2"/>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D129" s="1"/>
+    <row r="129" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E129" s="1"/>
       <c r="F129" s="2"/>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D130" s="1"/>
+    <row r="130" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E130" s="1"/>
       <c r="F130" s="2"/>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D131" s="1"/>
+    <row r="131" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E131" s="1"/>
       <c r="F131" s="2"/>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D132" s="1"/>
+    <row r="132" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E132" s="1"/>
       <c r="F132" s="2"/>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D133" s="1"/>
+    <row r="133" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E133" s="1"/>
       <c r="F133" s="2"/>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D134" s="1"/>
+    <row r="134" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E134" s="1"/>
       <c r="F134" s="2"/>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D135" s="1"/>
+    <row r="135" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E135" s="1"/>
       <c r="F135" s="2"/>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D136" s="1"/>
+    <row r="136" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E136" s="1"/>
       <c r="F136" s="2"/>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D137" s="1"/>
+    <row r="137" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E137" s="1"/>
       <c r="F137" s="2"/>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D138" s="1"/>
+    <row r="138" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E138" s="1"/>
       <c r="F138" s="2"/>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D139" s="1"/>
+    <row r="139" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E139" s="1"/>
       <c r="F139" s="2"/>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D140" s="1"/>
+    <row r="140" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E140" s="1"/>
       <c r="F140" s="2"/>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D141" s="1"/>
+    <row r="141" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E141" s="1"/>
       <c r="F141" s="2"/>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D142" s="1"/>
+    <row r="142" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E142" s="1"/>
       <c r="F142" s="2"/>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D143" s="1"/>
+    <row r="143" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E143" s="1"/>
       <c r="F143" s="2"/>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D144" s="1"/>
+    <row r="144" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E144" s="1"/>
       <c r="F144" s="2"/>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D145" s="1"/>
+    <row r="145" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E145" s="1"/>
       <c r="F145" s="2"/>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D146" s="1"/>
+    <row r="146" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E146" s="1"/>
       <c r="F146" s="2"/>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D147" s="1"/>
+    <row r="147" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E147" s="1"/>
       <c r="F147" s="2"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D148" s="1"/>
+    <row r="148" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E148" s="1"/>
       <c r="F148" s="2"/>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D149" s="1"/>
+    <row r="149" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E149" s="1"/>
       <c r="F149" s="2"/>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D150" s="1"/>
+    <row r="150" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E150" s="1"/>
       <c r="F150" s="2"/>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D151" s="1"/>
+    <row r="151" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E151" s="1"/>
       <c r="F151" s="2"/>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D152" s="1"/>
+    <row r="152" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E152" s="1"/>
       <c r="F152" s="2"/>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D153" s="1"/>
+    <row r="153" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E153" s="1"/>
       <c r="F153" s="2"/>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D154" s="1"/>
+    <row r="154" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E154" s="1"/>
       <c r="F154" s="2"/>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D155" s="1"/>
+    <row r="155" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E155" s="1"/>
       <c r="F155" s="2"/>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D156" s="1"/>
+    <row r="156" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E156" s="1"/>
       <c r="F156" s="2"/>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D157" s="1"/>
+    <row r="157" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E157" s="1"/>
       <c r="F157" s="2"/>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D158" s="1"/>
+    <row r="158" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E158" s="1"/>
       <c r="F158" s="2"/>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D159" s="1"/>
+    <row r="159" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E159" s="1"/>
       <c r="F159" s="2"/>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D160" s="1"/>
+    <row r="160" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E160" s="1"/>
       <c r="F160" s="2"/>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D161" s="1"/>
+    <row r="161" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E161" s="1"/>
       <c r="F161" s="2"/>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D162" s="1"/>
+    <row r="162" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E162" s="1"/>
       <c r="F162" s="2"/>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D163" s="1"/>
+    <row r="163" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E163" s="1"/>
       <c r="F163" s="2"/>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D164" s="1"/>
+    <row r="164" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E164" s="1"/>
       <c r="F164" s="2"/>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D165" s="1"/>
+    <row r="165" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E165" s="1"/>
       <c r="F165" s="2"/>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D166" s="1"/>
+    <row r="166" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E166" s="1"/>
       <c r="F166" s="2"/>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D167" s="1"/>
+    <row r="167" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E167" s="1"/>
       <c r="F167" s="2"/>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D168" s="1"/>
+    <row r="168" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E168" s="1"/>
       <c r="F168" s="2"/>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D169" s="1"/>
+    <row r="169" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E169" s="1"/>
       <c r="F169" s="2"/>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D170" s="1"/>
+    <row r="170" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E170" s="1"/>
       <c r="F170" s="2"/>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D171" s="1"/>
+    <row r="171" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E171" s="1"/>
       <c r="F171" s="2"/>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D172" s="1"/>
+    <row r="172" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E172" s="1"/>
       <c r="F172" s="2"/>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D173" s="1"/>
+    <row r="173" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E173" s="1"/>
       <c r="F173" s="2"/>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D174" s="1"/>
+    <row r="174" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E174" s="1"/>
       <c r="F174" s="2"/>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D175" s="1"/>
+    <row r="175" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E175" s="1"/>
       <c r="F175" s="2"/>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D176" s="1"/>
+    <row r="176" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E176" s="1"/>
       <c r="F176" s="2"/>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D177" s="1"/>
+    <row r="177" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E177" s="1"/>
       <c r="F177" s="2"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D178" s="1"/>
+    <row r="178" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E178" s="1"/>
       <c r="F178" s="2"/>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D179" s="1"/>
+    <row r="179" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E179" s="1"/>
       <c r="F179" s="2"/>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D180" s="1"/>
+    <row r="180" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E180" s="1"/>
       <c r="F180" s="2"/>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D181" s="1"/>
+    <row r="181" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E181" s="1"/>
       <c r="F181" s="2"/>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D182" s="1"/>
+    <row r="182" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E182" s="1"/>
       <c r="F182" s="2"/>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D183" s="1"/>
+    <row r="183" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E183" s="1"/>
       <c r="F183" s="2"/>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D184" s="1"/>
+    <row r="184" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E184" s="1"/>
       <c r="F184" s="2"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D185" s="1"/>
+    <row r="185" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E185" s="1"/>
       <c r="F185" s="2"/>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D186" s="1"/>
+    <row r="186" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E186" s="1"/>
       <c r="F186" s="2"/>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D187" s="1"/>
+    <row r="187" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E187" s="1"/>
       <c r="F187" s="2"/>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D188" s="1"/>
+    <row r="188" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E188" s="1"/>
       <c r="F188" s="2"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D189" s="1"/>
+    <row r="189" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E189" s="1"/>
       <c r="F189" s="2"/>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D190" s="1"/>
+    <row r="190" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E190" s="1"/>
       <c r="F190" s="2"/>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D191" s="1"/>
+    <row r="191" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E191" s="1"/>
       <c r="F191" s="2"/>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D192" s="1"/>
+    <row r="192" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E192" s="1"/>
       <c r="F192" s="2"/>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D193" s="1"/>
+    <row r="193" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E193" s="1"/>
       <c r="F193" s="2"/>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D194" s="1"/>
+    <row r="194" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E194" s="1"/>
       <c r="F194" s="2"/>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D195" s="1"/>
+    <row r="195" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E195" s="1"/>
       <c r="F195" s="2"/>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D196" s="1"/>
+    <row r="196" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E196" s="1"/>
       <c r="F196" s="2"/>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D197" s="1"/>
+    <row r="197" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E197" s="1"/>
       <c r="F197" s="2"/>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D198" s="1"/>
+    <row r="198" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E198" s="1"/>
       <c r="F198" s="2"/>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D199" s="1"/>
+    <row r="199" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E199" s="1"/>
       <c r="F199" s="2"/>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D200" s="1"/>
+    <row r="200" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E200" s="1"/>
       <c r="F200" s="2"/>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D201" s="1"/>
+    <row r="201" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E201" s="1"/>
       <c r="F201" s="2"/>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D202" s="1"/>
+    <row r="202" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E202" s="1"/>
       <c r="F202" s="2"/>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D203" s="1"/>
+    <row r="203" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E203" s="1"/>
       <c r="F203" s="2"/>
     </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D204" s="1"/>
+    <row r="204" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E204" s="1"/>
       <c r="F204" s="2"/>
     </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D205" s="1"/>
+    <row r="205" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E205" s="1"/>
       <c r="F205" s="2"/>
     </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D206" s="1"/>
+    <row r="206" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E206" s="1"/>
       <c r="F206" s="2"/>
     </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D207" s="1"/>
+    <row r="207" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E207" s="1"/>
       <c r="F207" s="2"/>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D208" s="1"/>
+    <row r="208" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E208" s="1"/>
       <c r="F208" s="2"/>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D209" s="1"/>
+    <row r="209" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E209" s="1"/>
       <c r="F209" s="2"/>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D210" s="1"/>
+    <row r="210" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E210" s="1"/>
       <c r="F210" s="2"/>
     </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D211" s="1"/>
+    <row r="211" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E211" s="1"/>
       <c r="F211" s="2"/>
     </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D212" s="1"/>
+    <row r="212" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E212" s="1"/>
       <c r="F212" s="2"/>
     </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D213" s="1"/>
+    <row r="213" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E213" s="1"/>
       <c r="F213" s="2"/>
     </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D214" s="1"/>
+    <row r="214" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E214" s="1"/>
       <c r="F214" s="2"/>
     </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D215" s="1"/>
+    <row r="215" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E215" s="1"/>
       <c r="F215" s="2"/>
     </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D216" s="1"/>
+    <row r="216" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E216" s="1"/>
       <c r="F216" s="2"/>
     </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D217" s="1"/>
+    <row r="217" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E217" s="1"/>
       <c r="F217" s="2"/>
     </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D218" s="1"/>
+    <row r="218" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E218" s="1"/>
       <c r="F218" s="2"/>
     </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D219" s="1"/>
+    <row r="219" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E219" s="1"/>
       <c r="F219" s="2"/>
     </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D220" s="1"/>
+    <row r="220" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E220" s="1"/>
       <c r="F220" s="2"/>
     </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D221" s="1"/>
+    <row r="221" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E221" s="1"/>
       <c r="F221" s="2"/>
     </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D222" s="1"/>
+    <row r="222" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E222" s="1"/>
       <c r="F222" s="2"/>
     </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D223" s="1"/>
+    <row r="223" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E223" s="1"/>
       <c r="F223" s="2"/>
     </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D224" s="1"/>
+    <row r="224" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E224" s="1"/>
       <c r="F224" s="2"/>
     </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D225" s="1"/>
+    <row r="225" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E225" s="1"/>
       <c r="F225" s="2"/>
     </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D226" s="1"/>
+    <row r="226" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E226" s="1"/>
       <c r="F226" s="2"/>
     </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D227" s="1"/>
+    <row r="227" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E227" s="1"/>
       <c r="F227" s="2"/>
     </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D228" s="1"/>
+    <row r="228" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E228" s="1"/>
       <c r="F228" s="2"/>
     </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D229" s="1"/>
+    <row r="229" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E229" s="1"/>
       <c r="F229" s="2"/>
     </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D230" s="1"/>
+    <row r="230" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E230" s="1"/>
       <c r="F230" s="2"/>
     </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D231" s="1"/>
+    <row r="231" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E231" s="1"/>
       <c r="F231" s="2"/>
     </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D232" s="1"/>
+    <row r="232" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E232" s="1"/>
       <c r="F232" s="2"/>
     </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D233" s="1"/>
+    <row r="233" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E233" s="1"/>
       <c r="F233" s="2"/>
     </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D234" s="1"/>
+    <row r="234" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E234" s="1"/>
       <c r="F234" s="2"/>
     </row>
-    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D235" s="1"/>
+    <row r="235" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E235" s="1"/>
       <c r="F235" s="2"/>
     </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D236" s="1"/>
+    <row r="236" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E236" s="1"/>
       <c r="F236" s="2"/>
     </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D237" s="1"/>
+    <row r="237" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E237" s="1"/>
       <c r="F237" s="2"/>
     </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D238" s="1"/>
+    <row r="238" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E238" s="1"/>
       <c r="F238" s="2"/>
     </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D239" s="1"/>
+    <row r="239" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E239" s="1"/>
       <c r="F239" s="2"/>
     </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D240" s="1"/>
+    <row r="240" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E240" s="1"/>
       <c r="F240" s="2"/>
     </row>
-    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D241" s="1"/>
+    <row r="241" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E241" s="1"/>
       <c r="F241" s="2"/>
     </row>
-    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D242" s="1"/>
+    <row r="242" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E242" s="1"/>
       <c r="F242" s="2"/>
     </row>
-    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D243" s="1"/>
+    <row r="243" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E243" s="1"/>
       <c r="F243" s="2"/>
     </row>
-    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D244" s="1"/>
+    <row r="244" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E244" s="1"/>
       <c r="F244" s="2"/>
     </row>
-    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D245" s="1"/>
+    <row r="245" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E245" s="1"/>
       <c r="F245" s="2"/>
     </row>
-    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D246" s="1"/>
+    <row r="246" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E246" s="1"/>
       <c r="F246" s="2"/>
     </row>
-    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D247" s="1"/>
+    <row r="247" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E247" s="1"/>
       <c r="F247" s="2"/>
     </row>
-    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D248" s="1"/>
+    <row r="248" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E248" s="1"/>
       <c r="F248" s="2"/>
     </row>
-    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D249" s="1"/>
+    <row r="249" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E249" s="1"/>
       <c r="F249" s="2"/>
     </row>
-    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D250" s="1"/>
+    <row r="250" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E250" s="1"/>
       <c r="F250" s="2"/>
     </row>
-    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D251" s="1"/>
+    <row r="251" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E251" s="1"/>
       <c r="F251" s="2"/>
     </row>
-    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D252" s="1"/>
+    <row r="252" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E252" s="1"/>
       <c r="F252" s="2"/>
     </row>
-    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D253" s="1"/>
+    <row r="253" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E253" s="1"/>
       <c r="F253" s="2"/>
     </row>
-    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D254" s="1"/>
+    <row r="254" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E254" s="1"/>
       <c r="F254" s="2"/>
     </row>
-    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D255" s="1"/>
+    <row r="255" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E255" s="1"/>
       <c r="F255" s="2"/>
     </row>
-    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D256" s="1"/>
+    <row r="256" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E256" s="1"/>
       <c r="F256" s="2"/>
     </row>
-    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D257" s="1"/>
+    <row r="257" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E257" s="1"/>
       <c r="F257" s="2"/>
     </row>
-    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D258" s="1"/>
+    <row r="258" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E258" s="1"/>
       <c r="F258" s="2"/>
     </row>
-    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D259" s="1"/>
+    <row r="259" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E259" s="1"/>
       <c r="F259" s="2"/>
     </row>
-    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D260" s="1"/>
+    <row r="260" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E260" s="1"/>
       <c r="F260" s="2"/>
     </row>
-    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D261" s="1"/>
+    <row r="261" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E261" s="1"/>
       <c r="F261" s="2"/>
     </row>
-    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D262" s="1"/>
+    <row r="262" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E262" s="1"/>
       <c r="F262" s="2"/>
     </row>
-    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D263" s="1"/>
+    <row r="263" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E263" s="1"/>
       <c r="F263" s="2"/>
     </row>
-    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D264" s="1"/>
+    <row r="264" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E264" s="1"/>
       <c r="F264" s="2"/>
     </row>
-    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D265" s="1"/>
+    <row r="265" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E265" s="1"/>
       <c r="F265" s="2"/>
     </row>
-    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D266" s="1"/>
+    <row r="266" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E266" s="1"/>
       <c r="F266" s="2"/>
     </row>
-    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D267" s="1"/>
+    <row r="267" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E267" s="1"/>
       <c r="F267" s="2"/>
     </row>
-    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D268" s="1"/>
+    <row r="268" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E268" s="1"/>
       <c r="F268" s="2"/>
     </row>
-    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D269" s="1"/>
+    <row r="269" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E269" s="1"/>
       <c r="F269" s="2"/>
     </row>
-    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D270" s="1"/>
+    <row r="270" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E270" s="1"/>
       <c r="F270" s="2"/>
     </row>
-    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D271" s="1"/>
+    <row r="271" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E271" s="1"/>
       <c r="F271" s="2"/>
     </row>
-    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D272" s="1"/>
+    <row r="272" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E272" s="1"/>
       <c r="F272" s="2"/>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D273" s="1"/>
+    <row r="273" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E273" s="1"/>
       <c r="F273" s="2"/>
     </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D274" s="1"/>
+    <row r="274" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E274" s="1"/>
       <c r="F274" s="2"/>
     </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D275" s="1"/>
+    <row r="275" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E275" s="1"/>
       <c r="F275" s="2"/>
     </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D276" s="1"/>
+    <row r="276" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E276" s="1"/>
       <c r="F276" s="2"/>
     </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D277" s="1"/>
+    <row r="277" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E277" s="1"/>
       <c r="F277" s="2"/>
     </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D278" s="1"/>
+    <row r="278" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E278" s="1"/>
       <c r="F278" s="2"/>
     </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D279" s="1"/>
+    <row r="279" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E279" s="1"/>
       <c r="F279" s="2"/>
     </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D280" s="1"/>
+    <row r="280" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E280" s="1"/>
       <c r="F280" s="2"/>
     </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D281" s="1"/>
+    <row r="281" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E281" s="1"/>
       <c r="F281" s="2"/>
     </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D282" s="1"/>
+    <row r="282" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E282" s="1"/>
       <c r="F282" s="2"/>
     </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D283" s="1"/>
+    <row r="283" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E283" s="1"/>
       <c r="F283" s="2"/>
     </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D284" s="1"/>
+    <row r="284" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E284" s="1"/>
       <c r="F284" s="2"/>
     </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D285" s="1"/>
+    <row r="285" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E285" s="1"/>
       <c r="F285" s="2"/>
     </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D286" s="1"/>
+    <row r="286" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E286" s="1"/>
       <c r="F286" s="2"/>
     </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D287" s="1"/>
+    <row r="287" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E287" s="1"/>
       <c r="F287" s="2"/>
     </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D288" s="1"/>
+    <row r="288" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E288" s="1"/>
       <c r="F288" s="2"/>
     </row>
-    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D289" s="1"/>
+    <row r="289" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E289" s="1"/>
       <c r="F289" s="2"/>
     </row>
-    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D290" s="1"/>
+    <row r="290" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E290" s="1"/>
       <c r="F290" s="2"/>
     </row>
-    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D291" s="1"/>
+    <row r="291" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E291" s="1"/>
       <c r="F291" s="2"/>
     </row>
-    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D292" s="1"/>
+    <row r="292" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E292" s="1"/>
       <c r="F292" s="2"/>
     </row>
-    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D293" s="1"/>
+    <row r="293" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E293" s="1"/>
       <c r="F293" s="2"/>
     </row>
-    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D294" s="1"/>
+    <row r="294" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E294" s="1"/>
       <c r="F294" s="2"/>
     </row>
-    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D295" s="1"/>
+    <row r="295" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E295" s="1"/>
       <c r="F295" s="2"/>
     </row>
-    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D296" s="1"/>
+    <row r="296" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E296" s="1"/>
       <c r="F296" s="2"/>
     </row>
-    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D297" s="1"/>
+    <row r="297" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E297" s="1"/>
       <c r="F297" s="2"/>
     </row>
-    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D298" s="1"/>
+    <row r="298" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E298" s="1"/>
       <c r="F298" s="2"/>
     </row>
-    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D299" s="1"/>
+    <row r="299" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E299" s="1"/>
       <c r="F299" s="2"/>
     </row>
-    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D300" s="1"/>
+    <row r="300" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E300" s="1"/>
       <c r="F300" s="2"/>
     </row>
-    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D301" s="1"/>
+    <row r="301" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E301" s="1"/>
       <c r="F301" s="2"/>
     </row>
-    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D302" s="1"/>
+    <row r="302" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E302" s="1"/>
       <c r="F302" s="2"/>
     </row>
-    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D303" s="1"/>
+    <row r="303" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E303" s="1"/>
       <c r="F303" s="2"/>
     </row>
-    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D304" s="1"/>
+    <row r="304" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E304" s="1"/>
       <c r="F304" s="2"/>
     </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D305" s="1"/>
+    <row r="305" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E305" s="1"/>
       <c r="F305" s="2"/>
     </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D306" s="1"/>
+    <row r="306" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E306" s="1"/>
       <c r="F306" s="2"/>
     </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D307" s="1"/>
+    <row r="307" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E307" s="1"/>
       <c r="F307" s="2"/>
     </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D308" s="1"/>
+    <row r="308" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E308" s="1"/>
       <c r="F308" s="2"/>
     </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D309" s="1"/>
+    <row r="309" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E309" s="1"/>
       <c r="F309" s="2"/>
     </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D310" s="1"/>
+    <row r="310" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E310" s="1"/>
       <c r="F310" s="2"/>
     </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D311" s="1"/>
+    <row r="311" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E311" s="1"/>
       <c r="F311" s="2"/>
     </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D312" s="1"/>
+    <row r="312" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E312" s="1"/>
       <c r="F312" s="2"/>
     </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D313" s="1"/>
+    <row r="313" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E313" s="1"/>
       <c r="F313" s="2"/>
     </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D314" s="1"/>
+    <row r="314" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E314" s="1"/>
       <c r="F314" s="2"/>
     </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D315" s="1"/>
+    <row r="315" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E315" s="1"/>
       <c r="F315" s="2"/>
     </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D316" s="1"/>
+    <row r="316" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E316" s="1"/>
       <c r="F316" s="2"/>
     </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D317" s="1"/>
+    <row r="317" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E317" s="1"/>
       <c r="F317" s="2"/>
     </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D318" s="1"/>
+    <row r="318" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E318" s="1"/>
       <c r="F318" s="2"/>
     </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D319" s="1"/>
+    <row r="319" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E319" s="1"/>
       <c r="F319" s="2"/>
     </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D320" s="1"/>
+    <row r="320" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E320" s="1"/>
       <c r="F320" s="2"/>
     </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D321" s="1"/>
+    <row r="321" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E321" s="1"/>
       <c r="F321" s="2"/>
     </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D322" s="1"/>
+    <row r="322" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E322" s="1"/>
       <c r="F322" s="2"/>
     </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D323" s="1"/>
+    <row r="323" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E323" s="1"/>
       <c r="F323" s="2"/>
     </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D324" s="1"/>
+    <row r="324" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E324" s="1"/>
       <c r="F324" s="2"/>
     </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D325" s="1"/>
+    <row r="325" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E325" s="1"/>
       <c r="F325" s="2"/>
     </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D326" s="1"/>
+    <row r="326" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E326" s="1"/>
       <c r="F326" s="2"/>
     </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D327" s="1"/>
+    <row r="327" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E327" s="1"/>
       <c r="F327" s="2"/>
     </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D328" s="1"/>
+    <row r="328" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E328" s="1"/>
       <c r="F328" s="2"/>
     </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D329" s="1"/>
+    <row r="329" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E329" s="1"/>
       <c r="F329" s="2"/>
     </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D330" s="1"/>
+    <row r="330" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E330" s="1"/>
       <c r="F330" s="2"/>
     </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D331" s="1"/>
+    <row r="331" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E331" s="1"/>
       <c r="F331" s="2"/>
     </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D332" s="1"/>
+    <row r="332" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E332" s="1"/>
       <c r="F332" s="2"/>
     </row>
-    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D333" s="1"/>
+    <row r="333" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E333" s="1"/>
       <c r="F333" s="2"/>
     </row>
-    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D334" s="1"/>
+    <row r="334" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E334" s="1"/>
       <c r="F334" s="2"/>
     </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D335" s="1"/>
+    <row r="335" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E335" s="1"/>
       <c r="F335" s="2"/>
     </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D336" s="1"/>
+    <row r="336" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E336" s="1"/>
       <c r="F336" s="2"/>
     </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D337" s="1"/>
+    <row r="337" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E337" s="1"/>
       <c r="F337" s="2"/>
     </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D338" s="1"/>
+    <row r="338" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E338" s="1"/>
       <c r="F338" s="2"/>
     </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D339" s="1"/>
+    <row r="339" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E339" s="1"/>
       <c r="F339" s="2"/>
     </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D340" s="1"/>
+    <row r="340" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E340" s="1"/>
       <c r="F340" s="2"/>
     </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D341" s="1"/>
+    <row r="341" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E341" s="1"/>
       <c r="F341" s="2"/>
     </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D342" s="1"/>
+    <row r="342" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E342" s="1"/>
       <c r="F342" s="2"/>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D343" s="1"/>
+    <row r="343" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E343" s="1"/>
       <c r="F343" s="2"/>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D344" s="1"/>
+    <row r="344" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E344" s="1"/>
       <c r="F344" s="2"/>
     </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D345" s="1"/>
+    <row r="345" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E345" s="1"/>
       <c r="F345" s="2"/>
     </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D346" s="1"/>
+    <row r="346" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E346" s="1"/>
       <c r="F346" s="2"/>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D347" s="1"/>
+    <row r="347" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E347" s="1"/>
       <c r="F347" s="2"/>
     </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D348" s="1"/>
+    <row r="348" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E348" s="1"/>
       <c r="F348" s="2"/>
     </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D349" s="1"/>
+    <row r="349" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E349" s="1"/>
       <c r="F349" s="2"/>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D350" s="1"/>
+    <row r="350" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E350" s="1"/>
       <c r="F350" s="2"/>
     </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D351" s="1"/>
+    <row r="351" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E351" s="1"/>
       <c r="F351" s="2"/>
     </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D352" s="1"/>
+    <row r="352" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E352" s="1"/>
       <c r="F352" s="2"/>
     </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D353" s="1"/>
+    <row r="353" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E353" s="1"/>
       <c r="F353" s="2"/>
     </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D354" s="1"/>
+    <row r="354" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E354" s="1"/>
       <c r="F354" s="2"/>
     </row>
-    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D355" s="1"/>
+    <row r="355" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E355" s="1"/>
       <c r="F355" s="2"/>
     </row>
-    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D356" s="1"/>
+    <row r="356" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E356" s="1"/>
       <c r="F356" s="2"/>
     </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D357" s="1"/>
+    <row r="357" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E357" s="1"/>
       <c r="F357" s="2"/>
     </row>
-    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D358" s="1"/>
+    <row r="358" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E358" s="1"/>
       <c r="F358" s="2"/>
     </row>
-    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D359" s="1"/>
+    <row r="359" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E359" s="1"/>
       <c r="F359" s="2"/>
     </row>
-    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D360" s="1"/>
+    <row r="360" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E360" s="1"/>
       <c r="F360" s="2"/>
     </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D361" s="1"/>
+    <row r="361" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E361" s="1"/>
       <c r="F361" s="2"/>
     </row>
-    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D362" s="1"/>
+    <row r="362" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E362" s="1"/>
       <c r="F362" s="2"/>
     </row>
-    <row r="363" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D363" s="1"/>
+    <row r="363" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E363" s="1"/>
       <c r="F363" s="2"/>
     </row>
-    <row r="364" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D364" s="1"/>
+    <row r="364" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E364" s="1"/>
       <c r="F364" s="2"/>
     </row>
-    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D365" s="1"/>
+    <row r="365" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E365" s="1"/>
       <c r="F365" s="2"/>
     </row>
-    <row r="366" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D366" s="1"/>
+    <row r="366" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E366" s="1"/>
       <c r="F366" s="2"/>
     </row>
-    <row r="367" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D367" s="1"/>
+    <row r="367" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E367" s="1"/>
       <c r="F367" s="2"/>
     </row>
-    <row r="368" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D368" s="1"/>
+    <row r="368" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E368" s="1"/>
       <c r="F368" s="2"/>
     </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D369" s="1"/>
+    <row r="369" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E369" s="1"/>
       <c r="F369" s="2"/>
     </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D370" s="1"/>
+    <row r="370" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E370" s="1"/>
       <c r="F370" s="2"/>
     </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D371" s="1"/>
+    <row r="371" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E371" s="1"/>
       <c r="F371" s="2"/>
     </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D372" s="1"/>
+    <row r="372" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E372" s="1"/>
       <c r="F372" s="2"/>
     </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D373" s="1"/>
+    <row r="373" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E373" s="1"/>
       <c r="F373" s="2"/>
     </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D374" s="1"/>
+    <row r="374" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E374" s="1"/>
       <c r="F374" s="2"/>
     </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D375" s="1"/>
+    <row r="375" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E375" s="1"/>
       <c r="F375" s="2"/>
     </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D376" s="1"/>
+    <row r="376" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E376" s="1"/>
       <c r="F376" s="2"/>
     </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D377" s="1"/>
+    <row r="377" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E377" s="1"/>
       <c r="F377" s="2"/>
     </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D378" s="1"/>
+    <row r="378" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E378" s="1"/>
       <c r="F378" s="2"/>
     </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D379" s="1"/>
+    <row r="379" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E379" s="1"/>
       <c r="F379" s="2"/>
     </row>
-    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D380" s="1"/>
+    <row r="380" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E380" s="1"/>
       <c r="F380" s="2"/>
     </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D381" s="1"/>
+    <row r="381" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E381" s="1"/>
       <c r="F381" s="2"/>
     </row>
-    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D382" s="1"/>
+    <row r="382" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E382" s="1"/>
       <c r="F382" s="2"/>
     </row>
-    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D383" s="1"/>
+    <row r="383" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E383" s="1"/>
       <c r="F383" s="2"/>
     </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D384" s="1"/>
+    <row r="384" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E384" s="1"/>
       <c r="F384" s="2"/>
     </row>
-    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D385" s="1"/>
+    <row r="385" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E385" s="1"/>
       <c r="F385" s="2"/>
     </row>
-    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D386" s="1"/>
+    <row r="386" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E386" s="1"/>
       <c r="F386" s="2"/>
     </row>
-    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D387" s="1"/>
+    <row r="387" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E387" s="1"/>
       <c r="F387" s="2"/>
     </row>
-    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D388" s="1"/>
+    <row r="388" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E388" s="1"/>
       <c r="F388" s="2"/>
     </row>
-    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D389" s="1"/>
+    <row r="389" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E389" s="1"/>
       <c r="F389" s="2"/>
     </row>
-    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D390" s="1"/>
+    <row r="390" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E390" s="1"/>
       <c r="F390" s="2"/>
     </row>
-    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D391" s="1"/>
+    <row r="391" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E391" s="1"/>
       <c r="F391" s="2"/>
     </row>
-    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D392" s="1"/>
+    <row r="392" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E392" s="1"/>
       <c r="F392" s="2"/>
     </row>
-    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D393" s="1"/>
+    <row r="393" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E393" s="1"/>
       <c r="F393" s="2"/>
     </row>
-    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D394" s="1"/>
+    <row r="394" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E394" s="1"/>
       <c r="F394" s="2"/>
     </row>
-    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D395" s="1"/>
+    <row r="395" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E395" s="1"/>
       <c r="F395" s="2"/>
     </row>
-    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D396" s="1"/>
+    <row r="396" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E396" s="1"/>
       <c r="F396" s="2"/>
     </row>
-    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D397" s="1"/>
+    <row r="397" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E397" s="1"/>
       <c r="F397" s="2"/>
     </row>
-    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D398" s="1"/>
+    <row r="398" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E398" s="1"/>
       <c r="F398" s="2"/>
     </row>
-    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D399" s="1"/>
+    <row r="399" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E399" s="1"/>
       <c r="F399" s="2"/>
     </row>
-    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D400" s="1"/>
+    <row r="400" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E400" s="1"/>
       <c r="F400" s="2"/>
     </row>
-    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D401" s="1"/>
+    <row r="401" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E401" s="1"/>
       <c r="F401" s="2"/>
     </row>
-    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D402" s="1"/>
+    <row r="402" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E402" s="1"/>
       <c r="F402" s="2"/>
     </row>
-    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D403" s="1"/>
+    <row r="403" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E403" s="1"/>
       <c r="F403" s="2"/>
     </row>
-    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D404" s="1"/>
+    <row r="404" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E404" s="1"/>
       <c r="F404" s="2"/>
     </row>
-    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D405" s="1"/>
+    <row r="405" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E405" s="1"/>
       <c r="F405" s="2"/>
     </row>
-    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D406" s="1"/>
+    <row r="406" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E406" s="1"/>
       <c r="F406" s="2"/>
     </row>
-    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D407" s="1"/>
+    <row r="407" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E407" s="1"/>
       <c r="F407" s="2"/>
     </row>
-    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D408" s="1"/>
+    <row r="408" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E408" s="1"/>
       <c r="F408" s="2"/>
     </row>
-    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D409" s="1"/>
+    <row r="409" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E409" s="1"/>
       <c r="F409" s="2"/>
     </row>
-    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D410" s="1"/>
+    <row r="410" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E410" s="1"/>
       <c r="F410" s="2"/>
     </row>
-    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D411" s="1"/>
+    <row r="411" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E411" s="1"/>
       <c r="F411" s="2"/>
     </row>
-    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D412" s="1"/>
+    <row r="412" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E412" s="1"/>
       <c r="F412" s="2"/>
     </row>
-    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D413" s="1"/>
+    <row r="413" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E413" s="1"/>
       <c r="F413" s="2"/>
     </row>
-    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D414" s="1"/>
+    <row r="414" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E414" s="1"/>
       <c r="F414" s="2"/>
     </row>
-    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D415" s="1"/>
+    <row r="415" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E415" s="1"/>
       <c r="F415" s="2"/>
     </row>
-    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D416" s="1"/>
+    <row r="416" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E416" s="1"/>
       <c r="F416" s="2"/>
     </row>
-    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D417" s="1"/>
+    <row r="417" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E417" s="1"/>
       <c r="F417" s="2"/>
     </row>
-    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D418" s="1"/>
+    <row r="418" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E418" s="1"/>
       <c r="F418" s="2"/>
     </row>
-    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D419" s="1"/>
+    <row r="419" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E419" s="1"/>
       <c r="F419" s="2"/>
     </row>
-    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D420" s="1"/>
+    <row r="420" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E420" s="1"/>
       <c r="F420" s="2"/>
     </row>
-    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D421" s="1"/>
+    <row r="421" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E421" s="1"/>
       <c r="F421" s="2"/>
     </row>
-    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D422" s="1"/>
+    <row r="422" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E422" s="1"/>
       <c r="F422" s="2"/>
     </row>
-    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D423" s="1"/>
+    <row r="423" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E423" s="1"/>
       <c r="F423" s="2"/>
     </row>
-    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D424" s="1"/>
+    <row r="424" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E424" s="1"/>
       <c r="F424" s="2"/>
     </row>
-    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D425" s="1"/>
+    <row r="425" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E425" s="1"/>
       <c r="F425" s="2"/>
     </row>
-    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D426" s="1"/>
+    <row r="426" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E426" s="1"/>
       <c r="F426" s="2"/>
     </row>
-    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D427" s="1"/>
+    <row r="427" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E427" s="1"/>
       <c r="F427" s="2"/>
     </row>
-    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D428" s="1"/>
+    <row r="428" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E428" s="1"/>
       <c r="F428" s="2"/>
     </row>
-    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D429" s="1"/>
+    <row r="429" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E429" s="1"/>
       <c r="F429" s="2"/>
     </row>
-    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D430" s="1"/>
+    <row r="430" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E430" s="1"/>
       <c r="F430" s="2"/>
     </row>
-    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D431" s="1"/>
+    <row r="431" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E431" s="1"/>
       <c r="F431" s="2"/>
     </row>
-    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D432" s="1"/>
+    <row r="432" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E432" s="1"/>
       <c r="F432" s="2"/>
     </row>
-    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D433" s="1"/>
+    <row r="433" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E433" s="1"/>
       <c r="F433" s="2"/>
     </row>
-    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D434" s="1"/>
+    <row r="434" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E434" s="1"/>
       <c r="F434" s="2"/>
     </row>
-    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D435" s="1"/>
+    <row r="435" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E435" s="1"/>
       <c r="F435" s="2"/>
     </row>
-    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D436" s="1"/>
+    <row r="436" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E436" s="1"/>
       <c r="F436" s="2"/>
     </row>
-    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D437" s="1"/>
+    <row r="437" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E437" s="1"/>
       <c r="F437" s="2"/>
     </row>
-    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D438" s="1"/>
+    <row r="438" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E438" s="1"/>
       <c r="F438" s="2"/>
     </row>
-    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D439" s="1"/>
+    <row r="439" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E439" s="1"/>
       <c r="F439" s="2"/>
     </row>
-    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D440" s="1"/>
+    <row r="440" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E440" s="1"/>
       <c r="F440" s="2"/>
     </row>
-    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D441" s="1"/>
+    <row r="441" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E441" s="1"/>
       <c r="F441" s="2"/>
     </row>
-    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D442" s="1"/>
+    <row r="442" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E442" s="1"/>
       <c r="F442" s="2"/>
     </row>
-    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D443" s="1"/>
+    <row r="443" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E443" s="1"/>
       <c r="F443" s="2"/>
     </row>
-    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D444" s="1"/>
+    <row r="444" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E444" s="1"/>
       <c r="F444" s="2"/>
     </row>
-    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D445" s="1"/>
+    <row r="445" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E445" s="1"/>
       <c r="F445" s="2"/>
     </row>
-    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D446" s="1"/>
+    <row r="446" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E446" s="1"/>
       <c r="F446" s="2"/>
     </row>
-    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D447" s="1"/>
+    <row r="447" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E447" s="1"/>
       <c r="F447" s="2"/>
     </row>
-    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D448" s="1"/>
+    <row r="448" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E448" s="1"/>
       <c r="F448" s="2"/>
     </row>
-    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D449" s="1"/>
+    <row r="449" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E449" s="1"/>
       <c r="F449" s="2"/>
     </row>
-    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D450" s="1"/>
+    <row r="450" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E450" s="1"/>
       <c r="F450" s="2"/>
     </row>
-    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D451" s="1"/>
+    <row r="451" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E451" s="1"/>
       <c r="F451" s="2"/>
     </row>
-    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D452" s="1"/>
+    <row r="452" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E452" s="1"/>
       <c r="F452" s="2"/>
     </row>
-    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D453" s="1"/>
+    <row r="453" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E453" s="1"/>
       <c r="F453" s="2"/>
     </row>
-    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D454" s="1"/>
+    <row r="454" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E454" s="1"/>
       <c r="F454" s="2"/>
     </row>
-    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D455" s="1"/>
+    <row r="455" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E455" s="1"/>
       <c r="F455" s="2"/>
     </row>
-    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D456" s="1"/>
+    <row r="456" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E456" s="1"/>
       <c r="F456" s="2"/>
     </row>
-    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D457" s="1"/>
+    <row r="457" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E457" s="1"/>
       <c r="F457" s="2"/>
     </row>
-    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D458" s="1"/>
+    <row r="458" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E458" s="1"/>
       <c r="F458" s="2"/>
     </row>
-    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D459" s="1"/>
+    <row r="459" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E459" s="1"/>
       <c r="F459" s="2"/>
     </row>
-    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D460" s="1"/>
+    <row r="460" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E460" s="1"/>
       <c r="F460" s="2"/>
     </row>
-    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D461" s="1"/>
+    <row r="461" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E461" s="1"/>
       <c r="F461" s="2"/>
     </row>
-    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D462" s="1"/>
+    <row r="462" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E462" s="1"/>
       <c r="F462" s="2"/>
     </row>
-    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D463" s="1"/>
+    <row r="463" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E463" s="1"/>
       <c r="F463" s="2"/>
     </row>
-    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D464" s="1"/>
+    <row r="464" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E464" s="1"/>
       <c r="F464" s="2"/>
     </row>
-    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D465" s="1"/>
+    <row r="465" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E465" s="1"/>
       <c r="F465" s="2"/>
     </row>
-    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D466" s="1"/>
+    <row r="466" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E466" s="1"/>
       <c r="F466" s="2"/>
     </row>
-    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D467" s="1"/>
+    <row r="467" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E467" s="1"/>
       <c r="F467" s="2"/>
     </row>
-    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D468" s="1"/>
+    <row r="468" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E468" s="1"/>
       <c r="F468" s="2"/>
     </row>
-    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D469" s="1"/>
+    <row r="469" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E469" s="1"/>
       <c r="F469" s="2"/>
     </row>
-    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D470" s="1"/>
+    <row r="470" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E470" s="1"/>
       <c r="F470" s="2"/>
     </row>
-    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D471" s="1"/>
+    <row r="471" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E471" s="1"/>
       <c r="F471" s="2"/>
     </row>
-    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D472" s="1"/>
+    <row r="472" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E472" s="1"/>
       <c r="F472" s="2"/>
     </row>
-    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D473" s="1"/>
+    <row r="473" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E473" s="1"/>
       <c r="F473" s="2"/>
     </row>
-    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D474" s="1"/>
+    <row r="474" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E474" s="1"/>
       <c r="F474" s="2"/>
     </row>
-    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D475" s="1"/>
+    <row r="475" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E475" s="1"/>
       <c r="F475" s="2"/>
     </row>
-    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D476" s="1"/>
+    <row r="476" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E476" s="1"/>
       <c r="F476" s="2"/>
     </row>
-    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D477" s="1"/>
+    <row r="477" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E477" s="1"/>
       <c r="F477" s="2"/>
     </row>
-    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D478" s="1"/>
+    <row r="478" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E478" s="1"/>
       <c r="F478" s="2"/>
     </row>
-    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D479" s="1"/>
+    <row r="479" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E479" s="1"/>
       <c r="F479" s="2"/>
     </row>
-    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D480" s="1"/>
+    <row r="480" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E480" s="1"/>
       <c r="F480" s="2"/>
     </row>
-    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D481" s="1"/>
+    <row r="481" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E481" s="1"/>
       <c r="F481" s="2"/>
     </row>
-    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D482" s="1"/>
+    <row r="482" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E482" s="1"/>
       <c r="F482" s="2"/>
     </row>
-    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D483" s="1"/>
+    <row r="483" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E483" s="1"/>
       <c r="F483" s="2"/>
     </row>
-    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D484" s="1"/>
+    <row r="484" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E484" s="1"/>
       <c r="F484" s="2"/>
     </row>
-    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D485" s="1"/>
+    <row r="485" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E485" s="1"/>
       <c r="F485" s="2"/>
     </row>
-    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D486" s="1"/>
+    <row r="486" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E486" s="1"/>
       <c r="F486" s="2"/>
     </row>
-    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D487" s="1"/>
+    <row r="487" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E487" s="1"/>
       <c r="F487" s="2"/>
     </row>
-    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D488" s="1"/>
+    <row r="488" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E488" s="1"/>
       <c r="F488" s="2"/>
     </row>
-    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D489" s="1"/>
+    <row r="489" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E489" s="1"/>
       <c r="F489" s="2"/>
     </row>
-    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D490" s="1"/>
+    <row r="490" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E490" s="1"/>
       <c r="F490" s="2"/>
     </row>
-    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D491" s="1"/>
+    <row r="491" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E491" s="1"/>
       <c r="F491" s="2"/>
     </row>
-    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D492" s="1"/>
+    <row r="492" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E492" s="1"/>
       <c r="F492" s="2"/>
     </row>
-    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D493" s="1"/>
+    <row r="493" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E493" s="1"/>
       <c r="F493" s="2"/>
     </row>
-    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D494" s="1"/>
+    <row r="494" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E494" s="1"/>
       <c r="F494" s="2"/>
     </row>
-    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D495" s="1"/>
+    <row r="495" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E495" s="1"/>
       <c r="F495" s="2"/>
     </row>
-    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D496" s="1"/>
+    <row r="496" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E496" s="1"/>
       <c r="F496" s="2"/>
     </row>
-    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D497" s="1"/>
+    <row r="497" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E497" s="1"/>
       <c r="F497" s="2"/>
     </row>
-    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D498" s="1"/>
+    <row r="498" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E498" s="1"/>
       <c r="F498" s="2"/>
     </row>
-    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D499" s="1"/>
+    <row r="499" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E499" s="1"/>
       <c r="F499" s="2"/>
     </row>
-    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D500" s="1"/>
+    <row r="500" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E500" s="1"/>
       <c r="F500" s="2"/>
     </row>
-    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D501" s="1"/>
+    <row r="501" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E501" s="1"/>
       <c r="F501" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A8:E100000">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="A8:E10 A14:E100000 B11:E13">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>IF(ISNUMBER($D8),$D8-TODAY()&lt;0,0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>IF(ISNUMBER($D8),$D8-TODAY()&lt;0,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>IF(ISNUMBER($D13),$D13-TODAY()&lt;0,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED682D6-73B7-DE4D-AA13-980ABD65EE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Калібрування пристрою" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Калібрування пристрою" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Звіт про калібрування пристрою</t>
   </si>
@@ -42,13 +28,16 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>Пристрій</t>
+    <t>Сайт</t>
   </si>
   <si>
-    <t>Сайт</t>
+    <t>Пристрій</t>
   </si>
   <si>
     <t>Серіал</t>
@@ -63,10 +52,10 @@
     <t>Дні до терміну</t>
   </si>
   <si>
-    <t>&lt;name&gt;</t>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
-    <t>&lt;siteName&gt;</t>
+    <t>&lt;name&gt;</t>
   </si>
   <si>
     <t>&lt;serial&gt;</t>
@@ -81,45 +70,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -145,18 +134,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
@@ -534,9 +515,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F501"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -546,2048 +527,2052 @@
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
-      <c r="F8" s="9" t="str">
-        <f ca="1">IF(ISNUMBER(E8),IF(E8-TODAY()&lt;0,"OVERDUE",INT(E8-TODAY())),"")</f>
-        <v/>
+      <c r="F8" s="9">
+        <f>IF(ISNUMBER(E8),IF(E8-TODAY()&lt;0,"OVERDUE",INT(E8-TODAY())),"")</f>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E9" s="1"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="1"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E11" s="1"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E12" s="1"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E13" s="1"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E14" s="1"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E15" s="1"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="1"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="1"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E20" s="1"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="1"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="1"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="1"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="1"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E29" s="1"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E30" s="1"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E32" s="1"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E34" s="1"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E35" s="1"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="1"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E38" s="1"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E39" s="1"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E40" s="1"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E41" s="1"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E42" s="1"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E43" s="1"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E44" s="1"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E45" s="1"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E46" s="1"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E47" s="1"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E48" s="1"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E49" s="1"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E50" s="1"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E51" s="1"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E52" s="1"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E53" s="1"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E54" s="1"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E55" s="1"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E56" s="1"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E57" s="1"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E58" s="1"/>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E59" s="1"/>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E60" s="1"/>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E61" s="1"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E62" s="1"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E63" s="1"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E64" s="1"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E65" s="1"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E66" s="1"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E67" s="1"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E68" s="1"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E69" s="1"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E70" s="1"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E71" s="1"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E72" s="1"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E73" s="1"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E74" s="1"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E75" s="1"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E76" s="1"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E77" s="1"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E78" s="1"/>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E79" s="1"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E80" s="1"/>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E81" s="1"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E82" s="1"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E83" s="1"/>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E84" s="1"/>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E85" s="1"/>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E86" s="1"/>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E87" s="1"/>
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E88" s="1"/>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E89" s="1"/>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E90" s="1"/>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E91" s="1"/>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E92" s="1"/>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E93" s="1"/>
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E94" s="1"/>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E95" s="1"/>
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E96" s="1"/>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E97" s="1"/>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E98" s="1"/>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E99" s="1"/>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E100" s="1"/>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E101" s="1"/>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E102" s="1"/>
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E103" s="1"/>
       <c r="F103" s="2"/>
     </row>
-    <row r="104" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E104" s="1"/>
       <c r="F104" s="2"/>
     </row>
-    <row r="105" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E105" s="1"/>
       <c r="F105" s="2"/>
     </row>
-    <row r="106" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E106" s="1"/>
       <c r="F106" s="2"/>
     </row>
-    <row r="107" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E107" s="1"/>
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E108" s="1"/>
       <c r="F108" s="2"/>
     </row>
-    <row r="109" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E109" s="1"/>
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E110" s="1"/>
       <c r="F110" s="2"/>
     </row>
-    <row r="111" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E111" s="1"/>
       <c r="F111" s="2"/>
     </row>
-    <row r="112" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E112" s="1"/>
       <c r="F112" s="2"/>
     </row>
-    <row r="113" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E113" s="1"/>
       <c r="F113" s="2"/>
     </row>
-    <row r="114" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E114" s="1"/>
       <c r="F114" s="2"/>
     </row>
-    <row r="115" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E115" s="1"/>
       <c r="F115" s="2"/>
     </row>
-    <row r="116" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E116" s="1"/>
       <c r="F116" s="2"/>
     </row>
-    <row r="117" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E117" s="1"/>
       <c r="F117" s="2"/>
     </row>
-    <row r="118" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E118" s="1"/>
       <c r="F118" s="2"/>
     </row>
-    <row r="119" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E119" s="1"/>
       <c r="F119" s="2"/>
     </row>
-    <row r="120" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E120" s="1"/>
       <c r="F120" s="2"/>
     </row>
-    <row r="121" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E121" s="1"/>
       <c r="F121" s="2"/>
     </row>
-    <row r="122" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E122" s="1"/>
       <c r="F122" s="2"/>
     </row>
-    <row r="123" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E123" s="1"/>
       <c r="F123" s="2"/>
     </row>
-    <row r="124" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E124" s="1"/>
       <c r="F124" s="2"/>
     </row>
-    <row r="125" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E125" s="1"/>
       <c r="F125" s="2"/>
     </row>
-    <row r="126" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E126" s="1"/>
       <c r="F126" s="2"/>
     </row>
-    <row r="127" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E127" s="1"/>
       <c r="F127" s="2"/>
     </row>
-    <row r="128" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E128" s="1"/>
       <c r="F128" s="2"/>
     </row>
-    <row r="129" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E129" s="1"/>
       <c r="F129" s="2"/>
     </row>
-    <row r="130" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E130" s="1"/>
       <c r="F130" s="2"/>
     </row>
-    <row r="131" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E131" s="1"/>
       <c r="F131" s="2"/>
     </row>
-    <row r="132" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E132" s="1"/>
       <c r="F132" s="2"/>
     </row>
-    <row r="133" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E133" s="1"/>
       <c r="F133" s="2"/>
     </row>
-    <row r="134" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E134" s="1"/>
       <c r="F134" s="2"/>
     </row>
-    <row r="135" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E135" s="1"/>
       <c r="F135" s="2"/>
     </row>
-    <row r="136" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E136" s="1"/>
       <c r="F136" s="2"/>
     </row>
-    <row r="137" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E137" s="1"/>
       <c r="F137" s="2"/>
     </row>
-    <row r="138" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E138" s="1"/>
       <c r="F138" s="2"/>
     </row>
-    <row r="139" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E139" s="1"/>
       <c r="F139" s="2"/>
     </row>
-    <row r="140" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E140" s="1"/>
       <c r="F140" s="2"/>
     </row>
-    <row r="141" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E141" s="1"/>
       <c r="F141" s="2"/>
     </row>
-    <row r="142" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E142" s="1"/>
       <c r="F142" s="2"/>
     </row>
-    <row r="143" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E143" s="1"/>
       <c r="F143" s="2"/>
     </row>
-    <row r="144" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E144" s="1"/>
       <c r="F144" s="2"/>
     </row>
-    <row r="145" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E145" s="1"/>
       <c r="F145" s="2"/>
     </row>
-    <row r="146" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E146" s="1"/>
       <c r="F146" s="2"/>
     </row>
-    <row r="147" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E147" s="1"/>
       <c r="F147" s="2"/>
     </row>
-    <row r="148" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E148" s="1"/>
       <c r="F148" s="2"/>
     </row>
-    <row r="149" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E149" s="1"/>
       <c r="F149" s="2"/>
     </row>
-    <row r="150" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E150" s="1"/>
       <c r="F150" s="2"/>
     </row>
-    <row r="151" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E151" s="1"/>
       <c r="F151" s="2"/>
     </row>
-    <row r="152" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E152" s="1"/>
       <c r="F152" s="2"/>
     </row>
-    <row r="153" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E153" s="1"/>
       <c r="F153" s="2"/>
     </row>
-    <row r="154" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E154" s="1"/>
       <c r="F154" s="2"/>
     </row>
-    <row r="155" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E155" s="1"/>
       <c r="F155" s="2"/>
     </row>
-    <row r="156" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E156" s="1"/>
       <c r="F156" s="2"/>
     </row>
-    <row r="157" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E157" s="1"/>
       <c r="F157" s="2"/>
     </row>
-    <row r="158" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E158" s="1"/>
       <c r="F158" s="2"/>
     </row>
-    <row r="159" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E159" s="1"/>
       <c r="F159" s="2"/>
     </row>
-    <row r="160" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E160" s="1"/>
       <c r="F160" s="2"/>
     </row>
-    <row r="161" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E161" s="1"/>
       <c r="F161" s="2"/>
     </row>
-    <row r="162" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E162" s="1"/>
       <c r="F162" s="2"/>
     </row>
-    <row r="163" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E163" s="1"/>
       <c r="F163" s="2"/>
     </row>
-    <row r="164" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E164" s="1"/>
       <c r="F164" s="2"/>
     </row>
-    <row r="165" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E165" s="1"/>
       <c r="F165" s="2"/>
     </row>
-    <row r="166" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E166" s="1"/>
       <c r="F166" s="2"/>
     </row>
-    <row r="167" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E167" s="1"/>
       <c r="F167" s="2"/>
     </row>
-    <row r="168" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E168" s="1"/>
       <c r="F168" s="2"/>
     </row>
-    <row r="169" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E169" s="1"/>
       <c r="F169" s="2"/>
     </row>
-    <row r="170" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E170" s="1"/>
       <c r="F170" s="2"/>
     </row>
-    <row r="171" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E171" s="1"/>
       <c r="F171" s="2"/>
     </row>
-    <row r="172" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E172" s="1"/>
       <c r="F172" s="2"/>
     </row>
-    <row r="173" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E173" s="1"/>
       <c r="F173" s="2"/>
     </row>
-    <row r="174" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E174" s="1"/>
       <c r="F174" s="2"/>
     </row>
-    <row r="175" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E175" s="1"/>
       <c r="F175" s="2"/>
     </row>
-    <row r="176" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E176" s="1"/>
       <c r="F176" s="2"/>
     </row>
-    <row r="177" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E177" s="1"/>
       <c r="F177" s="2"/>
     </row>
-    <row r="178" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E178" s="1"/>
       <c r="F178" s="2"/>
     </row>
-    <row r="179" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E179" s="1"/>
       <c r="F179" s="2"/>
     </row>
-    <row r="180" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E180" s="1"/>
       <c r="F180" s="2"/>
     </row>
-    <row r="181" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E181" s="1"/>
       <c r="F181" s="2"/>
     </row>
-    <row r="182" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E182" s="1"/>
       <c r="F182" s="2"/>
     </row>
-    <row r="183" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E183" s="1"/>
       <c r="F183" s="2"/>
     </row>
-    <row r="184" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E184" s="1"/>
       <c r="F184" s="2"/>
     </row>
-    <row r="185" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E185" s="1"/>
       <c r="F185" s="2"/>
     </row>
-    <row r="186" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E186" s="1"/>
       <c r="F186" s="2"/>
     </row>
-    <row r="187" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E187" s="1"/>
       <c r="F187" s="2"/>
     </row>
-    <row r="188" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E188" s="1"/>
       <c r="F188" s="2"/>
     </row>
-    <row r="189" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E189" s="1"/>
       <c r="F189" s="2"/>
     </row>
-    <row r="190" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E190" s="1"/>
       <c r="F190" s="2"/>
     </row>
-    <row r="191" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E191" s="1"/>
       <c r="F191" s="2"/>
     </row>
-    <row r="192" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E192" s="1"/>
       <c r="F192" s="2"/>
     </row>
-    <row r="193" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E193" s="1"/>
       <c r="F193" s="2"/>
     </row>
-    <row r="194" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E194" s="1"/>
       <c r="F194" s="2"/>
     </row>
-    <row r="195" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E195" s="1"/>
       <c r="F195" s="2"/>
     </row>
-    <row r="196" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E196" s="1"/>
       <c r="F196" s="2"/>
     </row>
-    <row r="197" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E197" s="1"/>
       <c r="F197" s="2"/>
     </row>
-    <row r="198" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E198" s="1"/>
       <c r="F198" s="2"/>
     </row>
-    <row r="199" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E199" s="1"/>
       <c r="F199" s="2"/>
     </row>
-    <row r="200" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E200" s="1"/>
       <c r="F200" s="2"/>
     </row>
-    <row r="201" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E201" s="1"/>
       <c r="F201" s="2"/>
     </row>
-    <row r="202" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E202" s="1"/>
       <c r="F202" s="2"/>
     </row>
-    <row r="203" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E203" s="1"/>
       <c r="F203" s="2"/>
     </row>
-    <row r="204" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E204" s="1"/>
       <c r="F204" s="2"/>
     </row>
-    <row r="205" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E205" s="1"/>
       <c r="F205" s="2"/>
     </row>
-    <row r="206" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E206" s="1"/>
       <c r="F206" s="2"/>
     </row>
-    <row r="207" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E207" s="1"/>
       <c r="F207" s="2"/>
     </row>
-    <row r="208" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E208" s="1"/>
       <c r="F208" s="2"/>
     </row>
-    <row r="209" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E209" s="1"/>
       <c r="F209" s="2"/>
     </row>
-    <row r="210" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E210" s="1"/>
       <c r="F210" s="2"/>
     </row>
-    <row r="211" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E211" s="1"/>
       <c r="F211" s="2"/>
     </row>
-    <row r="212" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E212" s="1"/>
       <c r="F212" s="2"/>
     </row>
-    <row r="213" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E213" s="1"/>
       <c r="F213" s="2"/>
     </row>
-    <row r="214" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E214" s="1"/>
       <c r="F214" s="2"/>
     </row>
-    <row r="215" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E215" s="1"/>
       <c r="F215" s="2"/>
     </row>
-    <row r="216" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E216" s="1"/>
       <c r="F216" s="2"/>
     </row>
-    <row r="217" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E217" s="1"/>
       <c r="F217" s="2"/>
     </row>
-    <row r="218" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E218" s="1"/>
       <c r="F218" s="2"/>
     </row>
-    <row r="219" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E219" s="1"/>
       <c r="F219" s="2"/>
     </row>
-    <row r="220" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E220" s="1"/>
       <c r="F220" s="2"/>
     </row>
-    <row r="221" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E221" s="1"/>
       <c r="F221" s="2"/>
     </row>
-    <row r="222" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E222" s="1"/>
       <c r="F222" s="2"/>
     </row>
-    <row r="223" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E223" s="1"/>
       <c r="F223" s="2"/>
     </row>
-    <row r="224" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E224" s="1"/>
       <c r="F224" s="2"/>
     </row>
-    <row r="225" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E225" s="1"/>
       <c r="F225" s="2"/>
     </row>
-    <row r="226" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E226" s="1"/>
       <c r="F226" s="2"/>
     </row>
-    <row r="227" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E227" s="1"/>
       <c r="F227" s="2"/>
     </row>
-    <row r="228" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E228" s="1"/>
       <c r="F228" s="2"/>
     </row>
-    <row r="229" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E229" s="1"/>
       <c r="F229" s="2"/>
     </row>
-    <row r="230" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E230" s="1"/>
       <c r="F230" s="2"/>
     </row>
-    <row r="231" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E231" s="1"/>
       <c r="F231" s="2"/>
     </row>
-    <row r="232" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E232" s="1"/>
       <c r="F232" s="2"/>
     </row>
-    <row r="233" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E233" s="1"/>
       <c r="F233" s="2"/>
     </row>
-    <row r="234" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E234" s="1"/>
       <c r="F234" s="2"/>
     </row>
-    <row r="235" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E235" s="1"/>
       <c r="F235" s="2"/>
     </row>
-    <row r="236" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E236" s="1"/>
       <c r="F236" s="2"/>
     </row>
-    <row r="237" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E237" s="1"/>
       <c r="F237" s="2"/>
     </row>
-    <row r="238" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E238" s="1"/>
       <c r="F238" s="2"/>
     </row>
-    <row r="239" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E239" s="1"/>
       <c r="F239" s="2"/>
     </row>
-    <row r="240" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E240" s="1"/>
       <c r="F240" s="2"/>
     </row>
-    <row r="241" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E241" s="1"/>
       <c r="F241" s="2"/>
     </row>
-    <row r="242" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E242" s="1"/>
       <c r="F242" s="2"/>
     </row>
-    <row r="243" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E243" s="1"/>
       <c r="F243" s="2"/>
     </row>
-    <row r="244" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E244" s="1"/>
       <c r="F244" s="2"/>
     </row>
-    <row r="245" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E245" s="1"/>
       <c r="F245" s="2"/>
     </row>
-    <row r="246" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E246" s="1"/>
       <c r="F246" s="2"/>
     </row>
-    <row r="247" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E247" s="1"/>
       <c r="F247" s="2"/>
     </row>
-    <row r="248" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E248" s="1"/>
       <c r="F248" s="2"/>
     </row>
-    <row r="249" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E249" s="1"/>
       <c r="F249" s="2"/>
     </row>
-    <row r="250" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E250" s="1"/>
       <c r="F250" s="2"/>
     </row>
-    <row r="251" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E251" s="1"/>
       <c r="F251" s="2"/>
     </row>
-    <row r="252" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E252" s="1"/>
       <c r="F252" s="2"/>
     </row>
-    <row r="253" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E253" s="1"/>
       <c r="F253" s="2"/>
     </row>
-    <row r="254" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E254" s="1"/>
       <c r="F254" s="2"/>
     </row>
-    <row r="255" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E255" s="1"/>
       <c r="F255" s="2"/>
     </row>
-    <row r="256" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E256" s="1"/>
       <c r="F256" s="2"/>
     </row>
-    <row r="257" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E257" s="1"/>
       <c r="F257" s="2"/>
     </row>
-    <row r="258" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E258" s="1"/>
       <c r="F258" s="2"/>
     </row>
-    <row r="259" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E259" s="1"/>
       <c r="F259" s="2"/>
     </row>
-    <row r="260" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E260" s="1"/>
       <c r="F260" s="2"/>
     </row>
-    <row r="261" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E261" s="1"/>
       <c r="F261" s="2"/>
     </row>
-    <row r="262" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E262" s="1"/>
       <c r="F262" s="2"/>
     </row>
-    <row r="263" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E263" s="1"/>
       <c r="F263" s="2"/>
     </row>
-    <row r="264" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E264" s="1"/>
       <c r="F264" s="2"/>
     </row>
-    <row r="265" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E265" s="1"/>
       <c r="F265" s="2"/>
     </row>
-    <row r="266" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E266" s="1"/>
       <c r="F266" s="2"/>
     </row>
-    <row r="267" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E267" s="1"/>
       <c r="F267" s="2"/>
     </row>
-    <row r="268" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E268" s="1"/>
       <c r="F268" s="2"/>
     </row>
-    <row r="269" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E269" s="1"/>
       <c r="F269" s="2"/>
     </row>
-    <row r="270" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E270" s="1"/>
       <c r="F270" s="2"/>
     </row>
-    <row r="271" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E271" s="1"/>
       <c r="F271" s="2"/>
     </row>
-    <row r="272" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E272" s="1"/>
       <c r="F272" s="2"/>
     </row>
-    <row r="273" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E273" s="1"/>
       <c r="F273" s="2"/>
     </row>
-    <row r="274" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E274" s="1"/>
       <c r="F274" s="2"/>
     </row>
-    <row r="275" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E275" s="1"/>
       <c r="F275" s="2"/>
     </row>
-    <row r="276" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E276" s="1"/>
       <c r="F276" s="2"/>
     </row>
-    <row r="277" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E277" s="1"/>
       <c r="F277" s="2"/>
     </row>
-    <row r="278" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E278" s="1"/>
       <c r="F278" s="2"/>
     </row>
-    <row r="279" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E279" s="1"/>
       <c r="F279" s="2"/>
     </row>
-    <row r="280" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E280" s="1"/>
       <c r="F280" s="2"/>
     </row>
-    <row r="281" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E281" s="1"/>
       <c r="F281" s="2"/>
     </row>
-    <row r="282" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E282" s="1"/>
       <c r="F282" s="2"/>
     </row>
-    <row r="283" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E283" s="1"/>
       <c r="F283" s="2"/>
     </row>
-    <row r="284" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E284" s="1"/>
       <c r="F284" s="2"/>
     </row>
-    <row r="285" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E285" s="1"/>
       <c r="F285" s="2"/>
     </row>
-    <row r="286" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E286" s="1"/>
       <c r="F286" s="2"/>
     </row>
-    <row r="287" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E287" s="1"/>
       <c r="F287" s="2"/>
     </row>
-    <row r="288" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E288" s="1"/>
       <c r="F288" s="2"/>
     </row>
-    <row r="289" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E289" s="1"/>
       <c r="F289" s="2"/>
     </row>
-    <row r="290" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E290" s="1"/>
       <c r="F290" s="2"/>
     </row>
-    <row r="291" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E291" s="1"/>
       <c r="F291" s="2"/>
     </row>
-    <row r="292" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E292" s="1"/>
       <c r="F292" s="2"/>
     </row>
-    <row r="293" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E293" s="1"/>
       <c r="F293" s="2"/>
     </row>
-    <row r="294" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E294" s="1"/>
       <c r="F294" s="2"/>
     </row>
-    <row r="295" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E295" s="1"/>
       <c r="F295" s="2"/>
     </row>
-    <row r="296" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E296" s="1"/>
       <c r="F296" s="2"/>
     </row>
-    <row r="297" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E297" s="1"/>
       <c r="F297" s="2"/>
     </row>
-    <row r="298" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E298" s="1"/>
       <c r="F298" s="2"/>
     </row>
-    <row r="299" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E299" s="1"/>
       <c r="F299" s="2"/>
     </row>
-    <row r="300" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E300" s="1"/>
       <c r="F300" s="2"/>
     </row>
-    <row r="301" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E301" s="1"/>
       <c r="F301" s="2"/>
     </row>
-    <row r="302" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E302" s="1"/>
       <c r="F302" s="2"/>
     </row>
-    <row r="303" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E303" s="1"/>
       <c r="F303" s="2"/>
     </row>
-    <row r="304" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E304" s="1"/>
       <c r="F304" s="2"/>
     </row>
-    <row r="305" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E305" s="1"/>
       <c r="F305" s="2"/>
     </row>
-    <row r="306" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E306" s="1"/>
       <c r="F306" s="2"/>
     </row>
-    <row r="307" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E307" s="1"/>
       <c r="F307" s="2"/>
     </row>
-    <row r="308" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E308" s="1"/>
       <c r="F308" s="2"/>
     </row>
-    <row r="309" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E309" s="1"/>
       <c r="F309" s="2"/>
     </row>
-    <row r="310" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E310" s="1"/>
       <c r="F310" s="2"/>
     </row>
-    <row r="311" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E311" s="1"/>
       <c r="F311" s="2"/>
     </row>
-    <row r="312" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E312" s="1"/>
       <c r="F312" s="2"/>
     </row>
-    <row r="313" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E313" s="1"/>
       <c r="F313" s="2"/>
     </row>
-    <row r="314" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E314" s="1"/>
       <c r="F314" s="2"/>
     </row>
-    <row r="315" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E315" s="1"/>
       <c r="F315" s="2"/>
     </row>
-    <row r="316" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E316" s="1"/>
       <c r="F316" s="2"/>
     </row>
-    <row r="317" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E317" s="1"/>
       <c r="F317" s="2"/>
     </row>
-    <row r="318" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E318" s="1"/>
       <c r="F318" s="2"/>
     </row>
-    <row r="319" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E319" s="1"/>
       <c r="F319" s="2"/>
     </row>
-    <row r="320" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E320" s="1"/>
       <c r="F320" s="2"/>
     </row>
-    <row r="321" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E321" s="1"/>
       <c r="F321" s="2"/>
     </row>
-    <row r="322" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E322" s="1"/>
       <c r="F322" s="2"/>
     </row>
-    <row r="323" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E323" s="1"/>
       <c r="F323" s="2"/>
     </row>
-    <row r="324" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E324" s="1"/>
       <c r="F324" s="2"/>
     </row>
-    <row r="325" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E325" s="1"/>
       <c r="F325" s="2"/>
     </row>
-    <row r="326" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E326" s="1"/>
       <c r="F326" s="2"/>
     </row>
-    <row r="327" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E327" s="1"/>
       <c r="F327" s="2"/>
     </row>
-    <row r="328" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E328" s="1"/>
       <c r="F328" s="2"/>
     </row>
-    <row r="329" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E329" s="1"/>
       <c r="F329" s="2"/>
     </row>
-    <row r="330" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E330" s="1"/>
       <c r="F330" s="2"/>
     </row>
-    <row r="331" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E331" s="1"/>
       <c r="F331" s="2"/>
     </row>
-    <row r="332" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E332" s="1"/>
       <c r="F332" s="2"/>
     </row>
-    <row r="333" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E333" s="1"/>
       <c r="F333" s="2"/>
     </row>
-    <row r="334" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E334" s="1"/>
       <c r="F334" s="2"/>
     </row>
-    <row r="335" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E335" s="1"/>
       <c r="F335" s="2"/>
     </row>
-    <row r="336" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E336" s="1"/>
       <c r="F336" s="2"/>
     </row>
-    <row r="337" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E337" s="1"/>
       <c r="F337" s="2"/>
     </row>
-    <row r="338" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E338" s="1"/>
       <c r="F338" s="2"/>
     </row>
-    <row r="339" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E339" s="1"/>
       <c r="F339" s="2"/>
     </row>
-    <row r="340" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E340" s="1"/>
       <c r="F340" s="2"/>
     </row>
-    <row r="341" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E341" s="1"/>
       <c r="F341" s="2"/>
     </row>
-    <row r="342" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E342" s="1"/>
       <c r="F342" s="2"/>
     </row>
-    <row r="343" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E343" s="1"/>
       <c r="F343" s="2"/>
     </row>
-    <row r="344" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E344" s="1"/>
       <c r="F344" s="2"/>
     </row>
-    <row r="345" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E345" s="1"/>
       <c r="F345" s="2"/>
     </row>
-    <row r="346" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E346" s="1"/>
       <c r="F346" s="2"/>
     </row>
-    <row r="347" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E347" s="1"/>
       <c r="F347" s="2"/>
     </row>
-    <row r="348" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E348" s="1"/>
       <c r="F348" s="2"/>
     </row>
-    <row r="349" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E349" s="1"/>
       <c r="F349" s="2"/>
     </row>
-    <row r="350" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E350" s="1"/>
       <c r="F350" s="2"/>
     </row>
-    <row r="351" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E351" s="1"/>
       <c r="F351" s="2"/>
     </row>
-    <row r="352" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E352" s="1"/>
       <c r="F352" s="2"/>
     </row>
-    <row r="353" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E353" s="1"/>
       <c r="F353" s="2"/>
     </row>
-    <row r="354" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E354" s="1"/>
       <c r="F354" s="2"/>
     </row>
-    <row r="355" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E355" s="1"/>
       <c r="F355" s="2"/>
     </row>
-    <row r="356" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E356" s="1"/>
       <c r="F356" s="2"/>
     </row>
-    <row r="357" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E357" s="1"/>
       <c r="F357" s="2"/>
     </row>
-    <row r="358" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E358" s="1"/>
       <c r="F358" s="2"/>
     </row>
-    <row r="359" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E359" s="1"/>
       <c r="F359" s="2"/>
     </row>
-    <row r="360" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E360" s="1"/>
       <c r="F360" s="2"/>
     </row>
-    <row r="361" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E361" s="1"/>
       <c r="F361" s="2"/>
     </row>
-    <row r="362" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E362" s="1"/>
       <c r="F362" s="2"/>
     </row>
-    <row r="363" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E363" s="1"/>
       <c r="F363" s="2"/>
     </row>
-    <row r="364" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E364" s="1"/>
       <c r="F364" s="2"/>
     </row>
-    <row r="365" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E365" s="1"/>
       <c r="F365" s="2"/>
     </row>
-    <row r="366" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E366" s="1"/>
       <c r="F366" s="2"/>
     </row>
-    <row r="367" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E367" s="1"/>
       <c r="F367" s="2"/>
     </row>
-    <row r="368" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E368" s="1"/>
       <c r="F368" s="2"/>
     </row>
-    <row r="369" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E369" s="1"/>
       <c r="F369" s="2"/>
     </row>
-    <row r="370" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E370" s="1"/>
       <c r="F370" s="2"/>
     </row>
-    <row r="371" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E371" s="1"/>
       <c r="F371" s="2"/>
     </row>
-    <row r="372" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E372" s="1"/>
       <c r="F372" s="2"/>
     </row>
-    <row r="373" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E373" s="1"/>
       <c r="F373" s="2"/>
     </row>
-    <row r="374" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E374" s="1"/>
       <c r="F374" s="2"/>
     </row>
-    <row r="375" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E375" s="1"/>
       <c r="F375" s="2"/>
     </row>
-    <row r="376" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E376" s="1"/>
       <c r="F376" s="2"/>
     </row>
-    <row r="377" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E377" s="1"/>
       <c r="F377" s="2"/>
     </row>
-    <row r="378" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E378" s="1"/>
       <c r="F378" s="2"/>
     </row>
-    <row r="379" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E379" s="1"/>
       <c r="F379" s="2"/>
     </row>
-    <row r="380" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E380" s="1"/>
       <c r="F380" s="2"/>
     </row>
-    <row r="381" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E381" s="1"/>
       <c r="F381" s="2"/>
     </row>
-    <row r="382" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E382" s="1"/>
       <c r="F382" s="2"/>
     </row>
-    <row r="383" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E383" s="1"/>
       <c r="F383" s="2"/>
     </row>
-    <row r="384" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E384" s="1"/>
       <c r="F384" s="2"/>
     </row>
-    <row r="385" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E385" s="1"/>
       <c r="F385" s="2"/>
     </row>
-    <row r="386" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E386" s="1"/>
       <c r="F386" s="2"/>
     </row>
-    <row r="387" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E387" s="1"/>
       <c r="F387" s="2"/>
     </row>
-    <row r="388" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="388" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E388" s="1"/>
       <c r="F388" s="2"/>
     </row>
-    <row r="389" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E389" s="1"/>
       <c r="F389" s="2"/>
     </row>
-    <row r="390" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E390" s="1"/>
       <c r="F390" s="2"/>
     </row>
-    <row r="391" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E391" s="1"/>
       <c r="F391" s="2"/>
     </row>
-    <row r="392" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E392" s="1"/>
       <c r="F392" s="2"/>
     </row>
-    <row r="393" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E393" s="1"/>
       <c r="F393" s="2"/>
     </row>
-    <row r="394" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E394" s="1"/>
       <c r="F394" s="2"/>
     </row>
-    <row r="395" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E395" s="1"/>
       <c r="F395" s="2"/>
     </row>
-    <row r="396" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E396" s="1"/>
       <c r="F396" s="2"/>
     </row>
-    <row r="397" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E397" s="1"/>
       <c r="F397" s="2"/>
     </row>
-    <row r="398" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E398" s="1"/>
       <c r="F398" s="2"/>
     </row>
-    <row r="399" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E399" s="1"/>
       <c r="F399" s="2"/>
     </row>
-    <row r="400" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E400" s="1"/>
       <c r="F400" s="2"/>
     </row>
-    <row r="401" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E401" s="1"/>
       <c r="F401" s="2"/>
     </row>
-    <row r="402" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E402" s="1"/>
       <c r="F402" s="2"/>
     </row>
-    <row r="403" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E403" s="1"/>
       <c r="F403" s="2"/>
     </row>
-    <row r="404" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E404" s="1"/>
       <c r="F404" s="2"/>
     </row>
-    <row r="405" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E405" s="1"/>
       <c r="F405" s="2"/>
     </row>
-    <row r="406" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E406" s="1"/>
       <c r="F406" s="2"/>
     </row>
-    <row r="407" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E407" s="1"/>
       <c r="F407" s="2"/>
     </row>
-    <row r="408" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E408" s="1"/>
       <c r="F408" s="2"/>
     </row>
-    <row r="409" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E409" s="1"/>
       <c r="F409" s="2"/>
     </row>
-    <row r="410" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E410" s="1"/>
       <c r="F410" s="2"/>
     </row>
-    <row r="411" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E411" s="1"/>
       <c r="F411" s="2"/>
     </row>
-    <row r="412" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E412" s="1"/>
       <c r="F412" s="2"/>
     </row>
-    <row r="413" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E413" s="1"/>
       <c r="F413" s="2"/>
     </row>
-    <row r="414" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E414" s="1"/>
       <c r="F414" s="2"/>
     </row>
-    <row r="415" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E415" s="1"/>
       <c r="F415" s="2"/>
     </row>
-    <row r="416" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E416" s="1"/>
       <c r="F416" s="2"/>
     </row>
-    <row r="417" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E417" s="1"/>
       <c r="F417" s="2"/>
     </row>
-    <row r="418" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E418" s="1"/>
       <c r="F418" s="2"/>
     </row>
-    <row r="419" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E419" s="1"/>
       <c r="F419" s="2"/>
     </row>
-    <row r="420" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E420" s="1"/>
       <c r="F420" s="2"/>
     </row>
-    <row r="421" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E421" s="1"/>
       <c r="F421" s="2"/>
     </row>
-    <row r="422" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E422" s="1"/>
       <c r="F422" s="2"/>
     </row>
-    <row r="423" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E423" s="1"/>
       <c r="F423" s="2"/>
     </row>
-    <row r="424" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E424" s="1"/>
       <c r="F424" s="2"/>
     </row>
-    <row r="425" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E425" s="1"/>
       <c r="F425" s="2"/>
     </row>
-    <row r="426" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E426" s="1"/>
       <c r="F426" s="2"/>
     </row>
-    <row r="427" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E427" s="1"/>
       <c r="F427" s="2"/>
     </row>
-    <row r="428" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E428" s="1"/>
       <c r="F428" s="2"/>
     </row>
-    <row r="429" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E429" s="1"/>
       <c r="F429" s="2"/>
     </row>
-    <row r="430" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E430" s="1"/>
       <c r="F430" s="2"/>
     </row>
-    <row r="431" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E431" s="1"/>
       <c r="F431" s="2"/>
     </row>
-    <row r="432" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E432" s="1"/>
       <c r="F432" s="2"/>
     </row>
-    <row r="433" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E433" s="1"/>
       <c r="F433" s="2"/>
     </row>
-    <row r="434" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E434" s="1"/>
       <c r="F434" s="2"/>
     </row>
-    <row r="435" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E435" s="1"/>
       <c r="F435" s="2"/>
     </row>
-    <row r="436" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E436" s="1"/>
       <c r="F436" s="2"/>
     </row>
-    <row r="437" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E437" s="1"/>
       <c r="F437" s="2"/>
     </row>
-    <row r="438" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E438" s="1"/>
       <c r="F438" s="2"/>
     </row>
-    <row r="439" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E439" s="1"/>
       <c r="F439" s="2"/>
     </row>
-    <row r="440" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E440" s="1"/>
       <c r="F440" s="2"/>
     </row>
-    <row r="441" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E441" s="1"/>
       <c r="F441" s="2"/>
     </row>
-    <row r="442" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E442" s="1"/>
       <c r="F442" s="2"/>
     </row>
-    <row r="443" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E443" s="1"/>
       <c r="F443" s="2"/>
     </row>
-    <row r="444" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E444" s="1"/>
       <c r="F444" s="2"/>
     </row>
-    <row r="445" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E445" s="1"/>
       <c r="F445" s="2"/>
     </row>
-    <row r="446" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E446" s="1"/>
       <c r="F446" s="2"/>
     </row>
-    <row r="447" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E447" s="1"/>
       <c r="F447" s="2"/>
     </row>
-    <row r="448" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="448" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E448" s="1"/>
       <c r="F448" s="2"/>
     </row>
-    <row r="449" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E449" s="1"/>
       <c r="F449" s="2"/>
     </row>
-    <row r="450" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E450" s="1"/>
       <c r="F450" s="2"/>
     </row>
-    <row r="451" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E451" s="1"/>
       <c r="F451" s="2"/>
     </row>
-    <row r="452" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E452" s="1"/>
       <c r="F452" s="2"/>
     </row>
-    <row r="453" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E453" s="1"/>
       <c r="F453" s="2"/>
     </row>
-    <row r="454" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E454" s="1"/>
       <c r="F454" s="2"/>
     </row>
-    <row r="455" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E455" s="1"/>
       <c r="F455" s="2"/>
     </row>
-    <row r="456" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E456" s="1"/>
       <c r="F456" s="2"/>
     </row>
-    <row r="457" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E457" s="1"/>
       <c r="F457" s="2"/>
     </row>
-    <row r="458" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="458" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E458" s="1"/>
       <c r="F458" s="2"/>
     </row>
-    <row r="459" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E459" s="1"/>
       <c r="F459" s="2"/>
     </row>
-    <row r="460" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E460" s="1"/>
       <c r="F460" s="2"/>
     </row>
-    <row r="461" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E461" s="1"/>
       <c r="F461" s="2"/>
     </row>
-    <row r="462" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E462" s="1"/>
       <c r="F462" s="2"/>
     </row>
-    <row r="463" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E463" s="1"/>
       <c r="F463" s="2"/>
     </row>
-    <row r="464" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E464" s="1"/>
       <c r="F464" s="2"/>
     </row>
-    <row r="465" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="465" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E465" s="1"/>
       <c r="F465" s="2"/>
     </row>
-    <row r="466" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E466" s="1"/>
       <c r="F466" s="2"/>
     </row>
-    <row r="467" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E467" s="1"/>
       <c r="F467" s="2"/>
     </row>
-    <row r="468" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E468" s="1"/>
       <c r="F468" s="2"/>
     </row>
-    <row r="469" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E469" s="1"/>
       <c r="F469" s="2"/>
     </row>
-    <row r="470" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E470" s="1"/>
       <c r="F470" s="2"/>
     </row>
-    <row r="471" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E471" s="1"/>
       <c r="F471" s="2"/>
     </row>
-    <row r="472" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="472" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E472" s="1"/>
       <c r="F472" s="2"/>
     </row>
-    <row r="473" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E473" s="1"/>
       <c r="F473" s="2"/>
     </row>
-    <row r="474" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E474" s="1"/>
       <c r="F474" s="2"/>
     </row>
-    <row r="475" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E475" s="1"/>
       <c r="F475" s="2"/>
     </row>
-    <row r="476" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E476" s="1"/>
       <c r="F476" s="2"/>
     </row>
-    <row r="477" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E477" s="1"/>
       <c r="F477" s="2"/>
     </row>
-    <row r="478" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E478" s="1"/>
       <c r="F478" s="2"/>
     </row>
-    <row r="479" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E479" s="1"/>
       <c r="F479" s="2"/>
     </row>
-    <row r="480" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E480" s="1"/>
       <c r="F480" s="2"/>
     </row>
-    <row r="481" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="481" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E481" s="1"/>
       <c r="F481" s="2"/>
     </row>
-    <row r="482" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="482" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E482" s="1"/>
       <c r="F482" s="2"/>
     </row>
-    <row r="483" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="483" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E483" s="1"/>
       <c r="F483" s="2"/>
     </row>
-    <row r="484" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="484" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E484" s="1"/>
       <c r="F484" s="2"/>
     </row>
-    <row r="485" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="485" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E485" s="1"/>
       <c r="F485" s="2"/>
     </row>
-    <row r="486" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="486" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E486" s="1"/>
       <c r="F486" s="2"/>
     </row>
-    <row r="487" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="487" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E487" s="1"/>
       <c r="F487" s="2"/>
     </row>
-    <row r="488" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E488" s="1"/>
       <c r="F488" s="2"/>
     </row>
-    <row r="489" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E489" s="1"/>
       <c r="F489" s="2"/>
     </row>
-    <row r="490" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E490" s="1"/>
       <c r="F490" s="2"/>
     </row>
-    <row r="491" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="491" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E491" s="1"/>
       <c r="F491" s="2"/>
     </row>
-    <row r="492" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="492" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E492" s="1"/>
       <c r="F492" s="2"/>
     </row>
-    <row r="493" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="493" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E493" s="1"/>
       <c r="F493" s="2"/>
     </row>
-    <row r="494" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="494" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E494" s="1"/>
       <c r="F494" s="2"/>
     </row>
-    <row r="495" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="495" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E495" s="1"/>
       <c r="F495" s="2"/>
     </row>
-    <row r="496" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="496" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E496" s="1"/>
       <c r="F496" s="2"/>
     </row>
-    <row r="497" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="497" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E497" s="1"/>
       <c r="F497" s="2"/>
     </row>
-    <row r="498" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="498" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E498" s="1"/>
       <c r="F498" s="2"/>
     </row>
-    <row r="499" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="499" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E499" s="1"/>
       <c r="F499" s="2"/>
     </row>
-    <row r="500" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="500" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E500" s="1"/>
       <c r="F500" s="2"/>
     </row>
-    <row r="501" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="501" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E501" s="1"/>
       <c r="F501" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:E10 A14:E100000 B11:E13">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>IF(ISNUMBER($D8),$D8-TODAY()&lt;0,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2597,11 +2582,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>IF(ISNUMBER($D13),$D13-TODAY()&lt;0,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -166,9 +166,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>

--- a/api/templates/device_calibration_report/uk.xlsx
+++ b/api/templates/device_calibration_report/uk.xlsx
@@ -28,7 +28,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -166,7 +166,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
